--- a/Results/Phase 2/Carbon dioxide/carbon dioxide acidification results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide acidification results.xlsx
@@ -2687,7 +2687,7 @@
         <v>0.0004599057451112966</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0004311209423424839</v>
+        <v>0.0004311209423424838</v>
       </c>
       <c r="F9" t="n">
         <v>0.0005410038850230547</v>
@@ -2702,7 +2702,7 @@
         <v>0.0005105310834983184</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0007699957564680624</v>
+        <v>0.0007699957564680623</v>
       </c>
       <c r="K9" t="n">
         <v>0.0006974102620696368</v>
@@ -2723,7 +2723,7 @@
         <v>0.0006231179564544832</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0004403126353836192</v>
+        <v>0.0004403126353836191</v>
       </c>
       <c r="R9" t="n">
         <v>0.0008309111795768476</v>
@@ -3054,7 +3054,7 @@
         <v>0.002587161767243047</v>
       </c>
       <c r="J13" t="n">
-        <v>0.002492645784905756</v>
+        <v>0.002492645784905755</v>
       </c>
       <c r="K13" t="n">
         <v>0.002587161767243047</v>
@@ -3327,13 +3327,13 @@
         <v>0.0003552639365236154</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0003552639365236178</v>
+        <v>0.0003552639365236177</v>
       </c>
       <c r="N16" t="n">
         <v>0.000300967150182718</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0003076485750664435</v>
+        <v>0.0003076485750664434</v>
       </c>
       <c r="P16" t="n">
         <v>0.0003039910214531612</v>
@@ -3360,7 +3360,7 @@
         <v>0.0003470378989688774</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0002696331801158479</v>
+        <v>0.0002696331801158478</v>
       </c>
       <c r="Y16" t="n">
         <v>0.0004248394108507085</v>
@@ -3372,7 +3372,7 @@
         <v>0.0003552639365236154</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0004284320562631797</v>
+        <v>0.0004284320562631798</v>
       </c>
     </row>
   </sheetData>
@@ -5014,13 +5014,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002179858807583405</v>
+        <v>0.002179858807583378</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000575207703321852</v>
+        <v>0.0005752077033218519</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00436987774813572</v>
+        <v>0.004369877748135694</v>
       </c>
       <c r="E2" t="n">
         <v>0.001272096140076661</v>
@@ -5029,70 +5029,70 @@
         <v>0.001351489888327542</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001971170065574599</v>
+        <v>0.001971170065574577</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003889461978192387</v>
+        <v>0.0003889461978192217</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00273165647014191</v>
+        <v>0.002731656470141886</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002997437551020664</v>
+        <v>0.002997437551020628</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00375444648147083</v>
+        <v>0.003754446481470808</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003556669795775838</v>
+        <v>0.003556669795775799</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009118977750020768</v>
+        <v>0.009118977750020758</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001621190238405452</v>
+        <v>0.001621190238405434</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001514441081269175</v>
+        <v>0.001514441081269162</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001854020260094403</v>
+        <v>0.001854020260094392</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001184038218834936</v>
+        <v>0.001184038218834917</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0005121749641097187</v>
+        <v>0.0005121749641097002</v>
       </c>
       <c r="S2" t="n">
-        <v>0.002721087887970475</v>
+        <v>0.002721087887970459</v>
       </c>
       <c r="T2" t="n">
-        <v>0.002430377416517337</v>
+        <v>0.002430377416517312</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00583616623138065</v>
+        <v>0.005836166231380617</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001188644824224041</v>
+        <v>0.00118864482422404</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003647722130577099</v>
+        <v>0.003647722130577081</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01102550642566586</v>
+        <v>0.01102550642566584</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01098519567936328</v>
+        <v>0.01098519567936327</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00151133044146783</v>
+        <v>0.001511330441467802</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003455461356096855</v>
+        <v>0.003455461356096829</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.009366046653369724</v>
+        <v>0.009366046653369715</v>
       </c>
     </row>
     <row r="3">
@@ -5102,85 +5102,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0003219307081630417</v>
+        <v>0.0003219307081630193</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004680703896404534</v>
+        <v>0.000468070389640454</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004676040124808552</v>
+        <v>0.0004676040124808579</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003815831646679953</v>
+        <v>0.0003815831646679956</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0003400689796492899</v>
+        <v>0.0003400689796492898</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004978103211042312</v>
+        <v>0.0004978103211042385</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0004676040124808552</v>
+        <v>0.0004676040124808579</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004676040124808552</v>
+        <v>0.0004676040124808579</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000464611407417997</v>
+        <v>0.0004646114074179877</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004676040124808552</v>
+        <v>0.0004676040124808579</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004676040124808552</v>
+        <v>0.0004676040124808579</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004834915824305052</v>
+        <v>0.000483491582430506</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0003546828310209074</v>
+        <v>0.0003546828310208975</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0003857145521629801</v>
+        <v>0.000385714552162979</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003781079274796564</v>
+        <v>0.0003781079274796633</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000293302579034588</v>
+        <v>0.0002933025790345614</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0004676040124808552</v>
+        <v>0.0004676040124808579</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004676040124808552</v>
+        <v>0.0004676040124808579</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0004676040124808552</v>
+        <v>0.0004676040124808579</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0003964356732612726</v>
+        <v>0.0003964356732612632</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0004182313550968069</v>
+        <v>0.0004182313550968059</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0004676326414563897</v>
+        <v>0.000467632641456371</v>
       </c>
       <c r="X3" t="n">
-        <v>0.000306653826830876</v>
+        <v>0.0003066538268308601</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0006123287999570523</v>
+        <v>0.0006123287999570472</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0003192247517468583</v>
+        <v>0.0003192247517468537</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0004676040124808552</v>
+        <v>0.0004676040124808579</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0006424663473308313</v>
+        <v>0.0006424663473308314</v>
       </c>
     </row>
     <row r="4">
@@ -5190,85 +5190,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003587799987898529</v>
+        <v>0.003587799987898496</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003003219891321207</v>
+        <v>0.003003219891321188</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00438603617522908</v>
+        <v>0.004386036175229035</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003251558468674095</v>
+        <v>0.003251558468674091</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00328297389904494</v>
+        <v>0.003282973899044915</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003511735391983254</v>
+        <v>0.003511735391983213</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002935033371597105</v>
+        <v>0.00293503337159708</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003788923756365815</v>
+        <v>0.003788923756365774</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003758940408631442</v>
+        <v>0.003758940408631401</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00416171870528852</v>
+        <v>0.004161718705288492</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004089631425763815</v>
+        <v>0.004089631425763748</v>
       </c>
       <c r="M4" t="n">
-        <v>0.006127124096432656</v>
+        <v>0.00612712409643261</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003384171854650713</v>
+        <v>0.003384171854650683</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003345263040386426</v>
+        <v>0.0033452630403864</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003469035663528185</v>
+        <v>0.00346903566352814</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003224835076815454</v>
+        <v>0.003224835076815407</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002979948809884763</v>
+        <v>0.002979948809884721</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003785071632266878</v>
+        <v>0.003785071632266823</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003679111079116927</v>
+        <v>0.003679111079116878</v>
       </c>
       <c r="U4" t="n">
-        <v>0.004920481109343198</v>
+        <v>0.004920481109343162</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002386815151010551</v>
+        <v>0.002386815151010557</v>
       </c>
       <c r="W4" t="n">
-        <v>0.004122818932608351</v>
+        <v>0.004122818932608315</v>
       </c>
       <c r="X4" t="n">
-        <v>0.006811934673851034</v>
+        <v>0.006811934673851014</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.006797241880176426</v>
+        <v>0.00679724188017639</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.003344129248705823</v>
+        <v>0.003344129248705774</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004052742137950307</v>
+        <v>0.004052742137950264</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.006221503622949794</v>
+        <v>0.006221503622949738</v>
       </c>
     </row>
     <row r="5">
@@ -5278,85 +5278,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00291060701255301</v>
+        <v>0.002910607012552991</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002964169598554194</v>
+        <v>0.002964169598554165</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002963703221394583</v>
+        <v>0.002963703221394546</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002926976946068946</v>
+        <v>0.002926976946068948</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002914322854535686</v>
+        <v>0.002914322854535622</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002974713066187411</v>
+        <v>0.002974713066187398</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002963703221394583</v>
+        <v>0.002963703221394546</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002963703221394583</v>
+        <v>0.002963703221394546</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002835755021234407</v>
+        <v>0.00283575502123441</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002963703221394583</v>
+        <v>0.002963703221394546</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002963703221394583</v>
+        <v>0.002963703221394546</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002979590791344211</v>
+        <v>0.002979590791344169</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002922544776739905</v>
+        <v>0.002922544776739856</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002933855474703322</v>
+        <v>0.002933855474703278</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002931082949327745</v>
+        <v>0.002931082949327697</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002900172395654169</v>
+        <v>0.00290017239565413</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002963703221394583</v>
+        <v>0.002963703221394546</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002963703221394583</v>
+        <v>0.002963703221394546</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002963703221394583</v>
+        <v>0.002963703221394546</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002937763197449858</v>
+        <v>0.002937763197449861</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002106008488165382</v>
+        <v>0.002106008488165419</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002963713656319991</v>
+        <v>0.002963713656319942</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002905038768697679</v>
+        <v>0.002905038768697621</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003016453706985378</v>
+        <v>0.003016453706985359</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00290962072321432</v>
+        <v>0.00290962072321425</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002963703221394583</v>
+        <v>0.002963703221394546</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003041861038850385</v>
+        <v>0.003041861038850386</v>
       </c>
     </row>
     <row r="6">
@@ -5366,82 +5366,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0008633906200019426</v>
+        <v>0.0008633906200019289</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0002788105234245989</v>
+        <v>0.000278810523424599</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001661626807332495</v>
+        <v>0.001661626807332484</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000527149100777524</v>
+        <v>0.0005271491007775251</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0005585645311483409</v>
+        <v>0.0005585645311483415</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0007773575130432318</v>
+        <v>0.0007773575130432055</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0002106240037005257</v>
+        <v>0.0002106240037005134</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001064514388469228</v>
+        <v>0.001064514388469213</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001149911956425091</v>
+        <v>0.001149911956425083</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001437309337391935</v>
+        <v>0.001437309337391922</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001365222057867211</v>
+        <v>0.001365222057867186</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003402714728536046</v>
+        <v>0.003402714728536042</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0006597624867541293</v>
+        <v>0.0006597624867541187</v>
       </c>
       <c r="O6" t="n">
-        <v>0.000610885161446403</v>
+        <v>0.0006108851614463897</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0007346577845881575</v>
+        <v>0.0007346577845881456</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0005004257089188603</v>
+        <v>0.0005004257089188472</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0002555394419881741</v>
+        <v>0.0002555394419881613</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001060662264370298</v>
+        <v>0.001060662264370284</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0009547017112203315</v>
+        <v>0.0009547017112203211</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002186103230403152</v>
+        <v>0.002186103230403138</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0004867107520476066</v>
+        <v>0.0004867107520476111</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001388441053668326</v>
+        <v>0.001388441053668313</v>
       </c>
       <c r="X6" t="n">
-        <v>0.004077556794911016</v>
+        <v>0.004077556794911005</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.004072832512279842</v>
+        <v>0.004072832512279824</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0006197198808092339</v>
+        <v>0.000619719880809218</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001328332770053715</v>
+        <v>0.001328332770053704</v>
       </c>
       <c r="AB6" t="n">
         <v>0.00349709425505317</v>
@@ -5454,22 +5454,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001861976446564518</v>
+        <v>0.0001861976446564382</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002397602306575839</v>
+        <v>0.0002397602306575842</v>
       </c>
       <c r="D7" t="n">
         <v>0.0002392938534979842</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002025675781723712</v>
+        <v>0.0002025675781723711</v>
       </c>
       <c r="F7" t="n">
         <v>0.000189913486639057</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002403351872473728</v>
+        <v>0.0002403351872473836</v>
       </c>
       <c r="H7" t="n">
         <v>0.0002392938534979842</v>
@@ -5478,10 +5478,10 @@
         <v>0.0002392938534979842</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002267265690281186</v>
+        <v>0.0002267265690280992</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002392938534979842</v>
+        <v>0.0002392938534979843</v>
       </c>
       <c r="L7" t="n">
         <v>0.0002392938534979842</v>
@@ -5490,49 +5490,49 @@
         <v>0.0002551814234475973</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001981354088433048</v>
+        <v>0.0001981354088432851</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001994775957632822</v>
+        <v>0.0001994775957632678</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001967050703877139</v>
+        <v>0.000196705070387696</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001757630277575767</v>
+        <v>0.0001757630277575809</v>
       </c>
       <c r="R7" t="n">
         <v>0.0002392938534979842</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002392938534979842</v>
+        <v>0.0002392938534979843</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0002392938534979842</v>
+        <v>0.0002392938534979843</v>
       </c>
       <c r="U7" t="n">
-        <v>0.000203385318509833</v>
+        <v>0.0002033853185098342</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0002059040892024314</v>
+        <v>0.0002059040892024348</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0002293357773799451</v>
+        <v>0.0002293357773799407</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0001706608897576456</v>
+        <v>0.0001706608897576206</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0002920443390887874</v>
+        <v>0.0002920443390888031</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001852113553177073</v>
+        <v>0.0001852113553176855</v>
       </c>
       <c r="AA7" t="n">
         <v>0.0002392938534979842</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0003174516709538093</v>
+        <v>0.0003174516709538094</v>
       </c>
     </row>
     <row r="8">
@@ -5542,85 +5542,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="S8" t="n">
-        <v>0.000466812248687908</v>
+        <v>0.0004668122486879088</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0004537215316148247</v>
+        <v>0.0004537215316148253</v>
       </c>
     </row>
     <row r="9">
@@ -5630,67 +5630,67 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002434381867914122</v>
+        <v>0.002434381867914103</v>
       </c>
       <c r="C9" t="n">
         <v>0.0007093573115763132</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004788001771145685</v>
+        <v>0.004788001771145689</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001467892272751941</v>
+        <v>0.001467892272751943</v>
       </c>
       <c r="F9" t="n">
         <v>0.001549027581854388</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002210103452930001</v>
+        <v>0.002210103452930005</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0005096827316471837</v>
+        <v>0.0005096827316471849</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003027400465655936</v>
+        <v>0.003027400465655935</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003316252349529398</v>
+        <v>0.003316252349529397</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004126595948816024</v>
+        <v>0.004126595948816029</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003914044753377751</v>
+        <v>0.003914044753377732</v>
       </c>
       <c r="M9" t="n">
-        <v>0.009874799323324279</v>
+        <v>0.009874799323324277</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001833979086285444</v>
+        <v>0.001833979086285442</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001719255447947518</v>
+        <v>0.001719255447947521</v>
       </c>
       <c r="P9" t="n">
-        <v>0.00208420220672053</v>
+        <v>0.002084202206720529</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.00136417050383567</v>
+        <v>0.001364170503835675</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0006421170552146303</v>
+        <v>0.0006421170552146305</v>
       </c>
       <c r="S9" t="n">
         <v>0.003016042378797863</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002703614965947548</v>
+        <v>0.002703614965947544</v>
       </c>
       <c r="U9" t="n">
-        <v>0.00636382638806614</v>
+        <v>0.006363826388066151</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001379313600641446</v>
+        <v>0.001379313600641451</v>
       </c>
       <c r="W9" t="n">
         <v>0.004011898969821131</v>
@@ -5702,10 +5702,10 @@
         <v>0.01189750373061961</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001715912434052675</v>
+        <v>0.001715912434052673</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003805275740657052</v>
+        <v>0.003805275740657047</v>
       </c>
       <c r="AB9" t="n">
         <v>0.01013300970529047</v>
@@ -5718,85 +5718,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0004376609845476553</v>
+        <v>0.0004376609845476554</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0005942165202388152</v>
+        <v>0.0005942165202388161</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0005942165202388152</v>
+        <v>0.0005942165202388161</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0005108553155833475</v>
+        <v>0.0005108553155833474</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0004620505073048268</v>
+        <v>0.0004620505073048276</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0006266793304285868</v>
+        <v>0.0006266793304285869</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0005942165202388152</v>
+        <v>0.0005942165202388161</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0005942165202388152</v>
+        <v>0.0005942165202388161</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0005942165202388152</v>
+        <v>0.0005942165202388161</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0005942165202388152</v>
+        <v>0.0005942165202388161</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0005942165202388152</v>
+        <v>0.0005942165202388161</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0005942165202388797</v>
+        <v>0.00059421652023888</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0004728597889068303</v>
+        <v>0.0004728597889068308</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0005062096723982983</v>
+        <v>0.000506209672398298</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0004980348101085003</v>
+        <v>0.000498034810108501</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0004068942485795958</v>
+        <v>0.0004068942485795961</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0005942165202388152</v>
+        <v>0.0005942165202388161</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0005942165202388152</v>
+        <v>0.0005942165202388161</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0005942165202388152</v>
+        <v>0.0005942165202388161</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0005177316932971289</v>
+        <v>0.0005177316932971296</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0005513479419525669</v>
+        <v>0.0005513479419525672</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0005942472878843997</v>
+        <v>0.0005942472878844001</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0004212428745044552</v>
+        <v>0.0004212428745044554</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0007497526820443448</v>
+        <v>0.000749752682044345</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0004347528850968064</v>
+        <v>0.0004347528850968066</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0005942165202388152</v>
+        <v>0.0005942165202388161</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0007577518682264273</v>
+        <v>0.0007577518682264274</v>
       </c>
     </row>
     <row r="11">
@@ -5806,85 +5806,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="H11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="I11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="J11" t="n">
-        <v>0.002564041016972194</v>
+        <v>0.002564041016972133</v>
       </c>
       <c r="K11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="M11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="N11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="O11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="P11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="R11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="S11" t="n">
-        <v>0.002677921390510974</v>
+        <v>0.002677921390510939</v>
       </c>
       <c r="T11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="U11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001954635385198487</v>
+        <v>0.00195463538519846</v>
       </c>
       <c r="W11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="X11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.002671486970124707</v>
+        <v>0.002671486970124638</v>
       </c>
     </row>
     <row r="12">
@@ -5894,85 +5894,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.003645031900857508</v>
+        <v>0.003645031900857496</v>
       </c>
       <c r="C12" t="n">
-        <v>0.002797138457729306</v>
+        <v>0.002797138457729271</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00480189594446436</v>
+        <v>0.004801895944464329</v>
       </c>
       <c r="E12" t="n">
-        <v>0.003169977683467478</v>
+        <v>0.003169977683467428</v>
       </c>
       <c r="F12" t="n">
-        <v>0.003209857751459167</v>
+        <v>0.003209857751459171</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003534793355671839</v>
+        <v>0.003534793355671829</v>
       </c>
       <c r="H12" t="n">
-        <v>0.002698993323238741</v>
+        <v>0.002698993323238693</v>
       </c>
       <c r="I12" t="n">
-        <v>0.003936515624281041</v>
+        <v>0.003936515624281009</v>
       </c>
       <c r="J12" t="n">
-        <v>0.003971047718612913</v>
+        <v>0.003971047718612879</v>
       </c>
       <c r="K12" t="n">
-        <v>0.004476798160818491</v>
+        <v>0.004476798160818468</v>
       </c>
       <c r="L12" t="n">
-        <v>0.004372323842305716</v>
+        <v>0.004372323842305688</v>
       </c>
       <c r="M12" t="n">
-        <v>0.007302186317239912</v>
+        <v>0.007302186317239859</v>
       </c>
       <c r="N12" t="n">
-        <v>0.003349918663246759</v>
+        <v>0.003349918663246732</v>
       </c>
       <c r="O12" t="n">
-        <v>0.003293529077161653</v>
+        <v>0.003293529077161617</v>
       </c>
       <c r="P12" t="n">
-        <v>0.003472909691030404</v>
+        <v>0.003472909691030362</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0031189957960209</v>
+        <v>0.003118995796020885</v>
       </c>
       <c r="R12" t="n">
-        <v>0.002764088161561715</v>
+        <v>0.002764088161561681</v>
       </c>
       <c r="S12" t="n">
-        <v>0.003930932835712575</v>
+        <v>0.003930932835712558</v>
       </c>
       <c r="T12" t="n">
-        <v>0.003777366816124035</v>
+        <v>0.003777366816123999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.005576453822668403</v>
+        <v>0.005576453822668371</v>
       </c>
       <c r="V12" t="n">
-        <v>0.002409587428319107</v>
+        <v>0.002409587428319121</v>
       </c>
       <c r="W12" t="n">
-        <v>0.004420421678478533</v>
+        <v>0.004420421678478496</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0083176908821517</v>
+        <v>0.008317690882151669</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.008296396978201883</v>
+        <v>0.00829639697820185</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.003291885900807257</v>
+        <v>0.003291885900807231</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.004318861106159403</v>
+        <v>0.004318861106159377</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.007429103287211389</v>
+        <v>0.007429103287211357</v>
       </c>
     </row>
     <row r="13">
@@ -5982,85 +5982,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.002663592802762694</v>
+        <v>0.002663592802762641</v>
       </c>
       <c r="C13" t="n">
-        <v>0.002740543830335169</v>
+        <v>0.002740543830335112</v>
       </c>
       <c r="D13" t="n">
-        <v>0.002740543830335169</v>
+        <v>0.002740543830335112</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002699569678066477</v>
+        <v>0.002699569678066443</v>
       </c>
       <c r="F13" t="n">
-        <v>0.002675580873512661</v>
+        <v>0.002675580873512654</v>
       </c>
       <c r="G13" t="n">
-        <v>0.002756500127191521</v>
+        <v>0.00275650012719149</v>
       </c>
       <c r="H13" t="n">
-        <v>0.002740543830335169</v>
+        <v>0.002740543830335112</v>
       </c>
       <c r="I13" t="n">
-        <v>0.002740543830335169</v>
+        <v>0.002740543830335112</v>
       </c>
       <c r="J13" t="n">
-        <v>0.002633097877182652</v>
+        <v>0.00263309787718262</v>
       </c>
       <c r="K13" t="n">
-        <v>0.002740543830335169</v>
+        <v>0.002740543830335112</v>
       </c>
       <c r="L13" t="n">
-        <v>0.002740543830335169</v>
+        <v>0.002740543830335112</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0027405438303352</v>
+        <v>0.002740543830335144</v>
       </c>
       <c r="N13" t="n">
-        <v>0.002680893910339647</v>
+        <v>0.002680893910339607</v>
       </c>
       <c r="O13" t="n">
-        <v>0.002697286226285305</v>
+        <v>0.002697286226285294</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0026932680735532</v>
+        <v>0.002693268073553154</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.002648470169523676</v>
+        <v>0.002648470169523675</v>
       </c>
       <c r="R13" t="n">
-        <v>0.002740543830335169</v>
+        <v>0.002740543830335112</v>
       </c>
       <c r="S13" t="n">
-        <v>0.002740543830335169</v>
+        <v>0.002740543830335112</v>
       </c>
       <c r="T13" t="n">
-        <v>0.002740543830335169</v>
+        <v>0.002740543830335112</v>
       </c>
       <c r="U13" t="n">
-        <v>0.002702949592604231</v>
+        <v>0.002702949592604234</v>
       </c>
       <c r="V13" t="n">
-        <v>0.002002621248876411</v>
+        <v>0.002002621248876388</v>
       </c>
       <c r="W13" t="n">
-        <v>0.002740558953415506</v>
+        <v>0.002740558953415475</v>
       </c>
       <c r="X13" t="n">
-        <v>0.002655522884103844</v>
+        <v>0.0026555228841038</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.002816993809716446</v>
+        <v>0.002816993809716444</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.002662163397918964</v>
+        <v>0.002662163397918939</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.002740543830335169</v>
+        <v>0.002740543830335112</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.002820925613173525</v>
+        <v>0.002820925613173516</v>
       </c>
     </row>
     <row r="14">
@@ -6070,85 +6070,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0003288420091445922</v>
+        <v>0.0003288420091445925</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0003288420091445922</v>
+        <v>0.0003288420091445925</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0003288420091445922</v>
+        <v>0.0003288420091445925</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0003288420091445922</v>
+        <v>0.0003288420091445925</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0003288420091445922</v>
+        <v>0.0003288420091445925</v>
       </c>
       <c r="G14" t="n">
-        <v>0.000320270359656238</v>
+        <v>0.0003202703596562381</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0003288420091445922</v>
+        <v>0.0003288420091445925</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0003288420091445922</v>
+        <v>0.0003288420091445925</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0003206090046878987</v>
+        <v>0.000320609004687899</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0003288420091445922</v>
+        <v>0.0003288420091445925</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0003288420091445922</v>
+        <v>0.0003288420091445925</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0003288420091445922</v>
+        <v>0.0003288420091445925</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0003288420091445922</v>
+        <v>0.0003288420091445925</v>
       </c>
       <c r="O14" t="n">
-        <v>0.000320270359656238</v>
+        <v>0.0003202703596562381</v>
       </c>
       <c r="P14" t="n">
-        <v>0.000320270359656238</v>
+        <v>0.0003202703596562381</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0003288420091445922</v>
+        <v>0.0003288420091445925</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0003288420091445922</v>
+        <v>0.0003288420091445925</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0003352764295308605</v>
+        <v>0.000335276429530861</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0003288420091445922</v>
+        <v>0.0003288420091445925</v>
       </c>
       <c r="U14" t="n">
-        <v>0.000320270359656238</v>
+        <v>0.0003202703596562381</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0003207876793383779</v>
+        <v>0.0003207876793383778</v>
       </c>
       <c r="W14" t="n">
-        <v>0.000320270359656238</v>
+        <v>0.0003202703596562381</v>
       </c>
       <c r="X14" t="n">
-        <v>0.000320270359656238</v>
+        <v>0.0003202703596562381</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0003288420091445922</v>
+        <v>0.0003288420091445925</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0003288420091445922</v>
+        <v>0.0003288420091445925</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0003288420091445922</v>
+        <v>0.0003288420091445925</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0003288420091445922</v>
+        <v>0.0003288420091445925</v>
       </c>
     </row>
     <row r="15">
@@ -6158,85 +6158,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.001302386939877402</v>
+        <v>0.001302386939877401</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0004544934967491924</v>
+        <v>0.000454493496749193</v>
       </c>
       <c r="D15" t="n">
-        <v>0.002459250983484251</v>
+        <v>0.002459250983484249</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0008273327224873648</v>
+        <v>0.0008273327224873673</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0008672127904790846</v>
+        <v>0.0008672127904790839</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001183576745203389</v>
+        <v>0.001183576745203382</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0003563483622586349</v>
+        <v>0.0003563483622586357</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001593870663300928</v>
+        <v>0.001593870663300929</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001727615706328673</v>
+        <v>0.001727615706328667</v>
       </c>
       <c r="K15" t="n">
         <v>0.002134153199838389</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002029678881325612</v>
+        <v>0.002029678881325605</v>
       </c>
       <c r="M15" t="n">
-        <v>0.004959541356259815</v>
+        <v>0.00495954135625981</v>
       </c>
       <c r="N15" t="n">
-        <v>0.001007273702266652</v>
+        <v>0.001007273702266651</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0009423124666931865</v>
+        <v>0.0009423124666931896</v>
       </c>
       <c r="P15" t="n">
-        <v>0.00112169308056193</v>
+        <v>0.001121693080561931</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0007763508350408058</v>
+        <v>0.0007763508350408055</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0004214432005816024</v>
+        <v>0.0004214432005816023</v>
       </c>
       <c r="S15" t="n">
-        <v>0.001588287874732466</v>
+        <v>0.001588287874732465</v>
       </c>
       <c r="T15" t="n">
-        <v>0.001434721855143924</v>
+        <v>0.001434721855143923</v>
       </c>
       <c r="U15" t="n">
-        <v>0.003225237212199945</v>
+        <v>0.00322523721219994</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0007757397224590067</v>
+        <v>0.0007757397224590055</v>
       </c>
       <c r="W15" t="n">
-        <v>0.002069205068010061</v>
+        <v>0.002069205068010063</v>
       </c>
       <c r="X15" t="n">
-        <v>0.005966474271683245</v>
+        <v>0.005966474271683249</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.005953752017221778</v>
+        <v>0.005953752017221772</v>
       </c>
       <c r="Z15" t="n">
         <v>0.0009492409398271481</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0019762161451793</v>
+        <v>0.001976216145179296</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.005086458326231275</v>
+        <v>0.005086458326231277</v>
       </c>
     </row>
     <row r="16">
@@ -6246,85 +6246,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0003209478417825836</v>
+        <v>0.000320947841782584</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0003978988693550655</v>
+        <v>0.0003978988693550658</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0003978988693550655</v>
+        <v>0.0003978988693550658</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0003569247170863612</v>
+        <v>0.0003569247170863614</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0003329359125325647</v>
+        <v>0.0003329359125325651</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0004052835167230632</v>
+        <v>0.0004052835167230634</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0003978988693550655</v>
+        <v>0.0003978988693550658</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0003978988693550655</v>
+        <v>0.0003978988693550658</v>
       </c>
       <c r="J16" t="n">
-        <v>0.000389665864898372</v>
+        <v>0.0003896658648983721</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0003978988693550655</v>
+        <v>0.0003978988693550658</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0003978988693550655</v>
+        <v>0.0003978988693550658</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0003978988693550973</v>
+        <v>0.0003978988693550977</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0003382489493595427</v>
+        <v>0.0003382489493595431</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0003460696158168457</v>
+        <v>0.0003460696158168459</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0003420514630847417</v>
+        <v>0.0003420514630847419</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0003058252085435785</v>
+        <v>0.0003058252085435786</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0003978988693550655</v>
+        <v>0.0003978988693550658</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0003978988693550655</v>
+        <v>0.0003978988693550658</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0003978988693550655</v>
+        <v>0.0003978988693550658</v>
       </c>
       <c r="U16" t="n">
-        <v>0.000351732982135784</v>
+        <v>0.0003517329821357843</v>
       </c>
       <c r="V16" t="n">
         <v>0.0003687735430163123</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0003893423429470502</v>
+        <v>0.0003893423429470503</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0003043062736353668</v>
+        <v>0.000304306273635367</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.0004743488487363504</v>
+        <v>0.0004743488487363507</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0003195184369388783</v>
+        <v>0.0003195184369388787</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0003978988693550655</v>
+        <v>0.0003978988693550658</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0004782806521934258</v>
+        <v>0.000478280652193426</v>
       </c>
     </row>
   </sheetData>
@@ -6490,85 +6490,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001862482282518618</v>
+        <v>0.001862482282518626</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0005705205442831794</v>
+        <v>0.000570520544283179</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003099347425288305</v>
+        <v>0.003099347425288293</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009198622209683491</v>
+        <v>0.0009198622209683518</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001527870371255464</v>
+        <v>0.00152787037125546</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001753116896327591</v>
+        <v>0.001753116896327569</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003890604557456506</v>
+        <v>0.0003890604557456523</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002720281375220524</v>
+        <v>0.002720281375220522</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002902773034223259</v>
+        <v>0.00290277303422325</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004404752215074144</v>
+        <v>0.00440475221507415</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002992089877944975</v>
+        <v>0.002992089877944965</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007549651585713582</v>
+        <v>0.007549651585713573</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001116494848745597</v>
+        <v>0.001116494848745592</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001145545327774885</v>
+        <v>0.001145545327774878</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001596551286937558</v>
+        <v>0.001596551286937555</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001196311131186776</v>
+        <v>0.001196311131186773</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0009133785923628943</v>
+        <v>0.0009133785923628869</v>
       </c>
       <c r="S2" t="n">
         <v>0.002575972888697628</v>
       </c>
       <c r="T2" t="n">
-        <v>0.002428119057785964</v>
+        <v>0.002428119057785959</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006271676506233138</v>
+        <v>0.006271676506233118</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001778254278094302</v>
+        <v>0.001778254278094293</v>
       </c>
       <c r="W2" t="n">
-        <v>0.00307491088947545</v>
+        <v>0.003074910889475454</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01322021920713001</v>
+        <v>0.01322021920713</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0168879309625953</v>
+        <v>0.01688793096259529</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001329891141718056</v>
+        <v>0.001329891141718059</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.00368341679018496</v>
+        <v>0.003683416790184956</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.008292434333207423</v>
+        <v>0.008292434333207407</v>
       </c>
     </row>
     <row r="3">
@@ -6578,85 +6578,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000318816471115255</v>
+        <v>0.0003188164711152404</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004649456071418987</v>
+        <v>0.0004649456071418979</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004636950633132717</v>
+        <v>0.0004636950633132707</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003783467862766233</v>
+        <v>0.0003783467862766219</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0003383270203219618</v>
+        <v>0.0003383270203219613</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004937365832015886</v>
+        <v>0.0004937365832015996</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0004636950633132717</v>
+        <v>0.0004636950633132707</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004636950633132717</v>
+        <v>0.0004636950633132707</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004613396484408453</v>
+        <v>0.000461339648440848</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004636950633132717</v>
+        <v>0.0004636950633132707</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004636950633132717</v>
+        <v>0.0004636950633132707</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004760658142375313</v>
+        <v>0.0004760658142375306</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0003513899166988147</v>
+        <v>0.0003513899166988001</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0003822523461168213</v>
+        <v>0.0003822523461168203</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003746872189256841</v>
+        <v>0.0003746872189256878</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002903445210565238</v>
+        <v>0.0002903445210565291</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0004636950633132717</v>
+        <v>0.0004636950633132707</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004636950633132717</v>
+        <v>0.0004636950633132707</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0004636950633132717</v>
+        <v>0.0004636950633132707</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0003928959614315746</v>
+        <v>0.0003928959614315818</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0004165180894395137</v>
+        <v>0.0004165180894395042</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0004637235361058824</v>
+        <v>0.0004637235361058807</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0003036229319084439</v>
+        <v>0.0003036229319084377</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0006075977801126908</v>
+        <v>0.0006075977801126957</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0003161252768846341</v>
+        <v>0.0003161252768846433</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0004636950633132717</v>
+        <v>0.0004636950633132707</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0006348691055314941</v>
+        <v>0.0006348691055314931</v>
       </c>
     </row>
     <row r="4">
@@ -6666,85 +6666,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003453119986968516</v>
+        <v>0.003453119986968563</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002983009839650102</v>
+        <v>0.002983009839650132</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003903942807504283</v>
+        <v>0.003903942807504275</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003104331859924761</v>
+        <v>0.003104331859924794</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003329213308859645</v>
+        <v>0.003329213308859665</v>
       </c>
       <c r="G4" t="n">
         <v>0.003413257587935088</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002916075032902391</v>
+        <v>0.002916075032902411</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003765777683472866</v>
+        <v>0.003765777683472883</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003720637594353702</v>
+        <v>0.003720637594353725</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004379747524544249</v>
+        <v>0.00437974752454427</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003864848690979339</v>
+        <v>0.003864848690979344</v>
       </c>
       <c r="M4" t="n">
-        <v>0.005533888173346449</v>
+        <v>0.005533888173346465</v>
       </c>
       <c r="N4" t="n">
         <v>0.003181216327184967</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003191804885663192</v>
+        <v>0.003191804885663185</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00335619126179863</v>
+        <v>0.003356191261798627</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003210308424884665</v>
+        <v>0.003210308424884669</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00310718283684497</v>
+        <v>0.003107182836844988</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003713178934691067</v>
+        <v>0.003713178934691066</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003659287949511105</v>
+        <v>0.003659287949511109</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005060219506139856</v>
+        <v>0.005060219506139854</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0026827087059442</v>
+        <v>0.002682708705944189</v>
       </c>
       <c r="W4" t="n">
-        <v>0.003895035977148779</v>
+        <v>0.003895035977148821</v>
       </c>
       <c r="X4" t="n">
-        <v>0.007592881726708873</v>
+        <v>0.007592881726708869</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.008929719593130103</v>
+        <v>0.0089297195931301</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.003258996770147642</v>
+        <v>0.003258996770147635</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004116829232520346</v>
+        <v>0.004116829232520392</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.005809368167388634</v>
+        <v>0.005809368167388623</v>
       </c>
     </row>
     <row r="5">
@@ -6754,85 +6754,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002890471925351125</v>
+        <v>0.002890471925351133</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00294452901478561</v>
+        <v>0.002944529014785631</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002943278470956982</v>
+        <v>0.002943278470957005</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002906955842774903</v>
+        <v>0.002906955842774931</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002895638725767644</v>
+        <v>0.002895638725767675</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002954228252190937</v>
+        <v>0.002954228252190969</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002943278470956982</v>
+        <v>0.002943278470957005</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002943278470956982</v>
+        <v>0.002943278470957005</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002830763793994253</v>
+        <v>0.002830763793994263</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002943278470956982</v>
+        <v>0.002943278470957005</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002943278470956982</v>
+        <v>0.002943278470957005</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002955649221881184</v>
+        <v>0.002955649221881214</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002902344563769624</v>
+        <v>0.002902344563769635</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002913593556887546</v>
+        <v>0.002913593556887556</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002910836156860579</v>
+        <v>0.002910836156860585</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002880094233889231</v>
+        <v>0.002880094233889273</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002943278470956982</v>
+        <v>0.002943278470957005</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002943278470956982</v>
+        <v>0.002943278470957005</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002943278470956982</v>
+        <v>0.002943278470957005</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002917473029686128</v>
+        <v>0.002917473029686162</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002186371855493165</v>
+        <v>0.002186371855493162</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002943288848955541</v>
+        <v>0.002943288848955582</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002884934058721786</v>
+        <v>0.00288493405872179</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002995729321439348</v>
+        <v>0.002995729321439381</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002889491016655658</v>
+        <v>0.002889491016655642</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002943278470956982</v>
+        <v>0.002943278470957005</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003018275561571517</v>
+        <v>0.003018275561571509</v>
       </c>
     </row>
     <row r="6">
@@ -6842,85 +6842,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0007465098048447166</v>
+        <v>0.0007465098048447167</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0002763996575262985</v>
+        <v>0.0002763996575262983</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001197332625380476</v>
+        <v>0.001197332625380464</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003977216778009596</v>
+        <v>0.0003977216778009608</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0006226031267358461</v>
+        <v>0.0006226031267358439</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0006966954254954006</v>
+        <v>0.000696695425495387</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0002094648507785898</v>
+        <v>0.0002094648507785896</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001059167501349062</v>
+        <v>0.001059167501349053</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00111462578736819</v>
+        <v>0.001114625787368197</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001673137342420453</v>
+        <v>0.001673137342420462</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001158238508855537</v>
+        <v>0.001158238508855528</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002827277991222643</v>
+        <v>0.002827277991222641</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0004746061450611634</v>
+        <v>0.0004746061450611544</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0004752427232235044</v>
+        <v>0.0004752427232234948</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0006396290993589404</v>
+        <v>0.0006396290993589262</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.000503698242760862</v>
+        <v>0.000503698242760852</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0004005726547211684</v>
+        <v>0.0004005726547211608</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001006568752567269</v>
+        <v>0.001006568752567261</v>
       </c>
       <c r="T6" t="n">
-        <v>0.000952677767387307</v>
+        <v>0.0009526777673872985</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002343657343700169</v>
+        <v>0.002343657343700158</v>
       </c>
       <c r="V6" t="n">
-        <v>0.000701696399969133</v>
+        <v>0.0007016963999691263</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001178473814709093</v>
+        <v>0.001178473814709116</v>
       </c>
       <c r="X6" t="n">
-        <v>0.004876319564269185</v>
+        <v>0.004876319564269176</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.006223109411006306</v>
+        <v>0.006223109411006291</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0005523865880238387</v>
+        <v>0.0005523865880238321</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001410219050396552</v>
+        <v>0.001410219050396559</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003102757985264833</v>
+        <v>0.003102757985264831</v>
       </c>
     </row>
     <row r="7">
@@ -6930,85 +6930,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001838617432273231</v>
+        <v>0.0001838617432273308</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002379188326618046</v>
+        <v>0.0002379188326618045</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000236668288833178</v>
+        <v>0.0002366682888331877</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000200345660651102</v>
+        <v>0.0002003456606511016</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001890285436438414</v>
+        <v>0.0001890285436438411</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002376660897512452</v>
+        <v>0.0002376660897512495</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000236668288833178</v>
+        <v>0.0002366682888331877</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000236668288833178</v>
+        <v>0.0002366682888331877</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002247519870087402</v>
+        <v>0.0002247519870087456</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000236668288833178</v>
+        <v>0.0002366682888331877</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000236668288833178</v>
+        <v>0.0002366682888331877</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002490390397573857</v>
+        <v>0.0002490390397573853</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001957343816458209</v>
+        <v>0.0001957343816458056</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001970313944478537</v>
+        <v>0.0001970313944478443</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001942739944208931</v>
+        <v>0.0001942739944208896</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001734840517654328</v>
+        <v>0.0001734840517654307</v>
       </c>
       <c r="R7" t="n">
-        <v>0.000236668288833178</v>
+        <v>0.0002366682888331877</v>
       </c>
       <c r="S7" t="n">
-        <v>0.000236668288833178</v>
+        <v>0.0002366682888331877</v>
       </c>
       <c r="T7" t="n">
-        <v>0.000236668288833178</v>
+        <v>0.0002366682888331877</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0002009108672464393</v>
+        <v>0.0002009108672464349</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0002053595495181076</v>
+        <v>0.0002053595495181082</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0002267266865158529</v>
+        <v>0.0002267266865158638</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0001683718962820979</v>
+        <v>0.0001683718962820837</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0002891191393155509</v>
+        <v>0.0002891191393155499</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001828808345318599</v>
+        <v>0.0001828808345318421</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.000236668288833178</v>
+        <v>0.0002366682888331877</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0003116653794477146</v>
+        <v>0.000311665379447714</v>
       </c>
     </row>
     <row r="8">
@@ -7018,85 +7018,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660477</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0004544727736730266</v>
+        <v>0.000454472773673027</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0004433654939660478</v>
+        <v>0.0004433654939660476</v>
       </c>
     </row>
     <row r="9">
@@ -7106,85 +7106,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002094921015595536</v>
+        <v>0.002094921015595547</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0007051019095553608</v>
+        <v>0.0007051019095553597</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003424183682566763</v>
+        <v>0.00342418368256676</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001090702033147548</v>
+        <v>0.001090702033147551</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001738601015711225</v>
+        <v>0.001738601015711216</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001977385708070341</v>
+        <v>0.001977385708070325</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0005114301730578691</v>
+        <v>0.0005114301730578676</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003016800265209703</v>
+        <v>0.003016800265209701</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003215455968167672</v>
+        <v>0.003215455968167667</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00482710611310925</v>
+        <v>0.004827106113109253</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003308913675753286</v>
+        <v>0.003308913675753295</v>
       </c>
       <c r="M9" t="n">
-        <v>0.008193643986496265</v>
+        <v>0.008193643986496257</v>
       </c>
       <c r="N9" t="n">
         <v>0.001293206090131921</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001324426726801166</v>
+        <v>0.001324426726801163</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001809124179551769</v>
+        <v>0.001809124179551774</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001378984887509869</v>
+        <v>0.001378984887509873</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001074916442111048</v>
+        <v>0.001074916442111047</v>
       </c>
       <c r="S9" t="n">
         <v>0.002861711503283342</v>
       </c>
       <c r="T9" t="n">
-        <v>0.002702812549142359</v>
+        <v>0.00270281254914236</v>
       </c>
       <c r="U9" t="n">
-        <v>0.006833495230634439</v>
+        <v>0.006833495230634428</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002012444908493831</v>
+        <v>0.002012444908493829</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003397921664467196</v>
+        <v>0.003397921664467193</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01430111484636283</v>
+        <v>0.01430111484636282</v>
       </c>
       <c r="Y9" t="n">
         <v>0.01824281563585568</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.001522543724211536</v>
+        <v>0.001522543724211544</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.004051884775298803</v>
+        <v>0.004051884775298805</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.008983891644625885</v>
+        <v>0.008983891644625871</v>
       </c>
     </row>
     <row r="10">
@@ -7194,85 +7194,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0004359387527568655</v>
+        <v>0.0004359387527568647</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0005916402089567932</v>
+        <v>0.0005916402089567921</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0005916402089567932</v>
+        <v>0.0005916402089567921</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0005087337764364461</v>
+        <v>0.0005087337764364454</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0004601952199112348</v>
+        <v>0.0004601952199112342</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0006239259202002945</v>
+        <v>0.0006239259202002938</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0005916402089567932</v>
+        <v>0.0005916402089567921</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0005916402089567932</v>
+        <v>0.0005916402089567921</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0005916402089567932</v>
+        <v>0.0005916402089567921</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0005916402089567932</v>
+        <v>0.0005916402089567921</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0005916402089567932</v>
+        <v>0.0005916402089567921</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0005916402089568817</v>
+        <v>0.000591640208956881</v>
       </c>
       <c r="N10" t="n">
-        <v>0.000470945532115112</v>
+        <v>0.0004709455321151115</v>
       </c>
       <c r="O10" t="n">
-        <v>0.000504113477284564</v>
+        <v>0.0005041134772845627</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0004959832124736816</v>
+        <v>0.0004959832124736805</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0004053398629019939</v>
+        <v>0.0004053398629019934</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0005916402089567932</v>
+        <v>0.0005916402089567921</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0005916402089567932</v>
+        <v>0.0005916402089567921</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0005916402089567932</v>
+        <v>0.0005916402089567921</v>
       </c>
       <c r="U10" t="n">
-        <v>0.000515552202486104</v>
+        <v>0.000515552202486103</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0005489829551646645</v>
+        <v>0.0005489829551646633</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0005916708087521416</v>
+        <v>0.000591670808752141</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0004196102107449596</v>
+        <v>0.0004196102107449586</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0007462928889481315</v>
+        <v>0.0007462928889481298</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0004330465182709609</v>
+        <v>0.0004330465182709605</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0005916402089567932</v>
+        <v>0.0005916402089567921</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0007542833994996939</v>
+        <v>0.0007542833994996933</v>
       </c>
     </row>
     <row r="11">
@@ -7282,85 +7282,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="H11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="I11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="J11" t="n">
-        <v>0.002556162249276804</v>
+        <v>0.002556162249276812</v>
       </c>
       <c r="K11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529038</v>
       </c>
       <c r="M11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="N11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="O11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="P11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="R11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="S11" t="n">
-        <v>0.002656344751003769</v>
+        <v>0.002656344751003794</v>
       </c>
       <c r="T11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="U11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="V11" t="n">
-        <v>0.002018918041311081</v>
+        <v>0.002018918041311096</v>
       </c>
       <c r="W11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="X11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.002650885240529012</v>
+        <v>0.002650885240529036</v>
       </c>
     </row>
     <row r="12">
@@ -7370,85 +7370,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.003462666784511628</v>
+        <v>0.003462666784511637</v>
       </c>
       <c r="C12" t="n">
-        <v>0.002779535345706181</v>
+        <v>0.002779535345706202</v>
       </c>
       <c r="D12" t="n">
-        <v>0.004116033193342799</v>
+        <v>0.004116033193342831</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002969067613674206</v>
+        <v>0.002969067613674235</v>
       </c>
       <c r="F12" t="n">
-        <v>0.003287526442046732</v>
+        <v>0.003287526442046761</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003404895191509933</v>
+        <v>0.00340489519150995</v>
       </c>
       <c r="H12" t="n">
-        <v>0.002684340761436554</v>
+        <v>0.002684340761436579</v>
       </c>
       <c r="I12" t="n">
-        <v>0.003915793882460445</v>
+        <v>0.003915793882460446</v>
       </c>
       <c r="J12" t="n">
-        <v>0.003918715221753691</v>
+        <v>0.003918715221753704</v>
       </c>
       <c r="K12" t="n">
-        <v>0.004805605249406628</v>
+        <v>0.004805605249406666</v>
       </c>
       <c r="L12" t="n">
-        <v>0.004059375053255803</v>
+        <v>0.004059375053255833</v>
       </c>
       <c r="M12" t="n">
-        <v>0.006460344237556218</v>
+        <v>0.006460344237556238</v>
       </c>
       <c r="N12" t="n">
-        <v>0.00306860350810137</v>
+        <v>0.0030686035081014</v>
       </c>
       <c r="O12" t="n">
-        <v>0.003083949245079366</v>
+        <v>0.003083949245079386</v>
       </c>
       <c r="P12" t="n">
-        <v>0.003322190370736537</v>
+        <v>0.003322190370736563</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.003110765968681408</v>
+        <v>0.003110765968681432</v>
       </c>
       <c r="R12" t="n">
-        <v>0.002961308594194407</v>
+        <v>0.002961308594194398</v>
       </c>
       <c r="S12" t="n">
-        <v>0.003839563811498794</v>
+        <v>0.00383956381149882</v>
       </c>
       <c r="T12" t="n">
-        <v>0.003761460934156511</v>
+        <v>0.003761460934156535</v>
       </c>
       <c r="U12" t="n">
-        <v>0.005791796530489037</v>
+        <v>0.005791796530489062</v>
       </c>
       <c r="V12" t="n">
-        <v>0.002790160480983995</v>
+        <v>0.002790160480983953</v>
       </c>
       <c r="W12" t="n">
-        <v>0.004103124743507621</v>
+        <v>0.00410312474350761</v>
       </c>
       <c r="X12" t="n">
-        <v>0.009462321500518364</v>
+        <v>0.009462321500518386</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.01139976769043207</v>
+        <v>0.01139976769043208</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.003181328788146926</v>
+        <v>0.003181328788146962</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.004424564245156809</v>
+        <v>0.004424564245156847</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.006848771060417241</v>
+        <v>0.00684877106041726</v>
       </c>
     </row>
     <row r="13">
@@ -7458,85 +7458,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.002647234808335485</v>
+        <v>0.002647234808335493</v>
       </c>
       <c r="C13" t="n">
-        <v>0.002723766034115662</v>
+        <v>0.002723766034115675</v>
       </c>
       <c r="D13" t="n">
-        <v>0.002723766034115662</v>
+        <v>0.002723766034115675</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002683015413917887</v>
+        <v>0.002683015413917904</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0026591574788726</v>
+        <v>0.002659157478872608</v>
       </c>
       <c r="G13" t="n">
-        <v>0.002739635282335646</v>
+        <v>0.002739635282335668</v>
       </c>
       <c r="H13" t="n">
-        <v>0.002723766034115662</v>
+        <v>0.002723766034115675</v>
       </c>
       <c r="I13" t="n">
-        <v>0.002723766034115662</v>
+        <v>0.002723766034115675</v>
       </c>
       <c r="J13" t="n">
-        <v>0.002629043042863451</v>
+        <v>0.002629043042863459</v>
       </c>
       <c r="K13" t="n">
-        <v>0.002723766034115662</v>
+        <v>0.002723766034115675</v>
       </c>
       <c r="L13" t="n">
-        <v>0.002723766034115662</v>
+        <v>0.002723766034115675</v>
       </c>
       <c r="M13" t="n">
-        <v>0.002723766034115706</v>
+        <v>0.002723766034115719</v>
       </c>
       <c r="N13" t="n">
-        <v>0.002664441530740589</v>
+        <v>0.002664441530740583</v>
       </c>
       <c r="O13" t="n">
-        <v>0.00268074441937362</v>
+        <v>0.002680744419373624</v>
       </c>
       <c r="P13" t="n">
-        <v>0.002676748187436676</v>
+        <v>0.002676748187436698</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.002632194675730054</v>
+        <v>0.002632194675730074</v>
       </c>
       <c r="R13" t="n">
-        <v>0.002723766034115662</v>
+        <v>0.002723766034115675</v>
       </c>
       <c r="S13" t="n">
-        <v>0.002723766034115662</v>
+        <v>0.002723766034115675</v>
       </c>
       <c r="T13" t="n">
-        <v>0.002723766034115662</v>
+        <v>0.002723766034115675</v>
       </c>
       <c r="U13" t="n">
-        <v>0.002686366843738824</v>
+        <v>0.002686366843738838</v>
       </c>
       <c r="V13" t="n">
-        <v>0.00207083170972883</v>
+        <v>0.002070831709728822</v>
       </c>
       <c r="W13" t="n">
-        <v>0.002723781074693339</v>
+        <v>0.00272378107469335</v>
       </c>
       <c r="X13" t="n">
-        <v>0.002639208914642047</v>
+        <v>0.002639208914642055</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.002799781759715097</v>
+        <v>0.002799781759715115</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.002645813201525557</v>
+        <v>0.002645813201525565</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.002723766034115662</v>
+        <v>0.002723766034115675</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.002803709298879116</v>
+        <v>0.002803709298879152</v>
       </c>
     </row>
     <row r="14">
@@ -7546,85 +7546,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0003235453116602786</v>
+        <v>0.0003235453116602782</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0003235453116602786</v>
+        <v>0.0003235453116602782</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0003235453116602786</v>
+        <v>0.0003235453116602782</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0003235453116602786</v>
+        <v>0.0003235453116602782</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0003235453116602786</v>
+        <v>0.0003235453116602782</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0003149878764915734</v>
+        <v>0.000314987876491573</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0003235453116602786</v>
+        <v>0.0003235453116602782</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0003235453116602786</v>
+        <v>0.0003235453116602782</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0003153241669577306</v>
+        <v>0.0003153241669577301</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0003235453116602786</v>
+        <v>0.0003235453116602782</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0003235453116602786</v>
+        <v>0.0003235453116602782</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0003235453116602786</v>
+        <v>0.0003235453116602782</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0003235453116602786</v>
+        <v>0.0003235453116602782</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0003149878764915734</v>
+        <v>0.000314987876491573</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0003149878764915734</v>
+        <v>0.000314987876491573</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0003235453116602786</v>
+        <v>0.0003235453116602782</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0003235453116602786</v>
+        <v>0.0003235453116602782</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0003290048221350348</v>
+        <v>0.0003290048221350347</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0003235453116602786</v>
+        <v>0.0003235453116602782</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0003149878764915734</v>
+        <v>0.000314987876491573</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0003154998432559428</v>
+        <v>0.0003154998432559426</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0003149878764915734</v>
+        <v>0.000314987876491573</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0003149878764915734</v>
+        <v>0.000314987876491573</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0003235453116602786</v>
+        <v>0.0003235453116602782</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0003235453116602786</v>
+        <v>0.0003235453116602782</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0003235453116602786</v>
+        <v>0.0003235453116602782</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0003235453116602786</v>
+        <v>0.0003235453116602782</v>
       </c>
     </row>
     <row r="15">
@@ -7634,55 +7634,55 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.001135326855642891</v>
+        <v>0.001135326855642896</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0004521954168374468</v>
+        <v>0.0004521954168374466</v>
       </c>
       <c r="D15" t="n">
-        <v>0.001788693264474058</v>
+        <v>0.001788693264474055</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0006417276848054734</v>
+        <v>0.000641727684805474</v>
       </c>
       <c r="F15" t="n">
-        <v>0.000960186513178001</v>
+        <v>0.0009601865131779983</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001068997827472495</v>
+        <v>0.001068997827472488</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0003570008325678187</v>
+        <v>0.0003570008325678186</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001588453953591707</v>
+        <v>0.001588453953591709</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001677877139434621</v>
+        <v>0.00167787713943462</v>
       </c>
       <c r="K15" t="n">
-        <v>0.002478265320537896</v>
+        <v>0.002478265320537902</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001732035124387071</v>
+        <v>0.001732035124387073</v>
       </c>
       <c r="M15" t="n">
-        <v>0.004133004308687491</v>
+        <v>0.004133004308687486</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0007412635792326383</v>
+        <v>0.0007412635792326377</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0007480518810419283</v>
+        <v>0.0007480518810419263</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0009862930066990977</v>
+        <v>0.0009862930066990945</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0007834260398126756</v>
+        <v>0.0007834260398126753</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0006339686653256751</v>
+        <v>0.0006339686653256757</v>
       </c>
       <c r="S15" t="n">
         <v>0.001512223882630059</v>
@@ -7691,28 +7691,28 @@
         <v>0.001434121005287778</v>
       </c>
       <c r="U15" t="n">
-        <v>0.003455899166451595</v>
+        <v>0.003455899166451592</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0010867422829288</v>
+        <v>0.001086742282928797</v>
       </c>
       <c r="W15" t="n">
-        <v>0.001767227379470179</v>
+        <v>0.001767227379470176</v>
       </c>
       <c r="X15" t="n">
-        <v>0.007126424136480919</v>
+        <v>0.007126424136480927</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.009072427761563336</v>
+        <v>0.009072427761563327</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.000853988859278197</v>
+        <v>0.0008539888592782004</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.002097224316288074</v>
+        <v>0.002097224316288076</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.004521431131548505</v>
+        <v>0.004521431131548503</v>
       </c>
     </row>
     <row r="16">
@@ -7722,85 +7722,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0003198948794667537</v>
+        <v>0.0003198948794667535</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0003964261052469275</v>
+        <v>0.000396426105246927</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0003964261052469275</v>
+        <v>0.000396426105246927</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0003556754850491548</v>
+        <v>0.0003556754850491541</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0003318175500038667</v>
+        <v>0.0003318175500038662</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0004037379182982084</v>
+        <v>0.0004037379182982078</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0003964261052469275</v>
+        <v>0.000396426105246927</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0003964261052469275</v>
+        <v>0.000396426105246927</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0003882049605443799</v>
+        <v>0.0003882049605443793</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0003964261052469275</v>
+        <v>0.000396426105246927</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0003964261052469275</v>
+        <v>0.000396426105246927</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0003964261052469709</v>
+        <v>0.0003964261052469702</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0003371016018718583</v>
+        <v>0.0003371016018718578</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0003448470553361819</v>
+        <v>0.0003448470553361813</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0003408508233992414</v>
+        <v>0.0003408508233992411</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0003048547468613215</v>
+        <v>0.000304854746861321</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0003964261052469275</v>
+        <v>0.000396426105246927</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0003964261052469275</v>
+        <v>0.000396426105246927</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0003964261052469275</v>
+        <v>0.000396426105246927</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0003504694797013874</v>
+        <v>0.0003504694797013867</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0003674135116736683</v>
+        <v>0.0003674135116736675</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0003878837106559011</v>
+        <v>0.0003878837106559003</v>
       </c>
       <c r="X16" t="n">
-        <v>0.00030331155060461</v>
+        <v>0.0003033115506046098</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.0004724418308463616</v>
+        <v>0.0004724418308463609</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.000318473272656823</v>
+        <v>0.0003184732726568225</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0003964261052469275</v>
+        <v>0.000396426105246927</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0004763693700103838</v>
+        <v>0.0004763693700103829</v>
       </c>
     </row>
   </sheetData>
@@ -9545,7 +9545,7 @@
         <v>0.0002934558160669244</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004344479838552575</v>
+        <v>0.0004344479838552576</v>
       </c>
       <c r="H3" t="n">
         <v>0.0004070818019185345</v>
@@ -9621,7 +9621,7 @@
         <v>0.002758266908890319</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002785025039334314</v>
+        <v>0.002785025039334313</v>
       </c>
       <c r="D4" t="n">
         <v>0.002854878062295936</v>
@@ -9630,7 +9630,7 @@
         <v>0.002817915099987768</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002813464182574821</v>
+        <v>0.00281346418257482</v>
       </c>
       <c r="G4" t="n">
         <v>0.002804602997042765</v>
@@ -9666,7 +9666,7 @@
         <v>0.002753083925661932</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002905523396354361</v>
+        <v>0.00290552339635436</v>
       </c>
       <c r="S4" t="n">
         <v>0.002847708435482699</v>
@@ -9678,7 +9678,7 @@
         <v>0.002766340056536508</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002051124457007443</v>
+        <v>0.002051124457007444</v>
       </c>
       <c r="W4" t="n">
         <v>0.002967717715165055</v>
@@ -9693,7 +9693,7 @@
         <v>0.00287254078236939</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002984531599945073</v>
+        <v>0.002984531599945072</v>
       </c>
       <c r="AB4" t="n">
         <v>0.002718026463978899</v>
@@ -9706,7 +9706,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002748100237428968</v>
+        <v>0.002748100237428967</v>
       </c>
       <c r="C5" t="n">
         <v>0.002800805073146686</v>
@@ -9778,13 +9778,13 @@
         <v>0.002843991672565005</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002747206683243692</v>
+        <v>0.002747206683243693</v>
       </c>
       <c r="AA5" t="n">
         <v>0.002796204112993632</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002842575112269816</v>
+        <v>0.002842575112269815</v>
       </c>
     </row>
     <row r="6">
@@ -9800,7 +9800,7 @@
         <v>0.0001896095727796859</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0002594625957413096</v>
+        <v>0.0002594625957413097</v>
       </c>
       <c r="E6" t="n">
         <v>0.00022249963343315</v>
@@ -10064,7 +10064,7 @@
         <v>0.0004850210250307131</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0007045505067993304</v>
+        <v>0.0007045505067993306</v>
       </c>
       <c r="E9" t="n">
         <v>0.0006084226360638224</v>
@@ -10161,7 +10161,7 @@
         <v>0.0004118096625228293</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005609593776281437</v>
+        <v>0.0005609593776281436</v>
       </c>
       <c r="H10" t="n">
         <v>0.0005315488600800698</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.002530908211828594</v>
+        <v>0.002530908211828593</v>
       </c>
       <c r="C12" t="n">
         <v>0.002563020052940845</v>
@@ -10334,7 +10334,7 @@
         <v>0.002623675083318278</v>
       </c>
       <c r="F12" t="n">
-        <v>0.002614107018635966</v>
+        <v>0.002614107018635965</v>
       </c>
       <c r="G12" t="n">
         <v>0.00259806196300622</v>
@@ -10382,7 +10382,7 @@
         <v>0.002542608425848993</v>
       </c>
       <c r="V12" t="n">
-        <v>0.001971753828031273</v>
+        <v>0.001971753828031272</v>
       </c>
       <c r="W12" t="n">
         <v>0.002834460106029244</v>
@@ -10397,7 +10397,7 @@
         <v>0.002696522521790804</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.002858828055070001</v>
+        <v>0.00285882805507</v>
       </c>
       <c r="AB12" t="n">
         <v>0.00247820832211226</v>
@@ -10476,7 +10476,7 @@
         <v>0.002585903368387194</v>
       </c>
       <c r="X13" t="n">
-        <v>0.002508862755017048</v>
+        <v>0.002508862755017049</v>
       </c>
       <c r="Y13" t="n">
         <v>0.002655147000192184</v>

--- a/Results/Phase 2/Carbon dioxide/carbon dioxide acidification results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide acidification results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003446510182440745</v>
+        <v>0.003446510182440731</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008061667110948236</v>
+        <v>0.000806166711094823</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003695507925583774</v>
+        <v>0.00369550792558376</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001434094921109529</v>
+        <v>0.001434094921109522</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002203397416869048</v>
+        <v>0.002203397416869047</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002231539333095914</v>
+        <v>0.002231539333095898</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002495354914105024</v>
+        <v>0.002495354914105008</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003688223837569509</v>
+        <v>0.003688223837569526</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003190895603167191</v>
+        <v>0.003190895603167187</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005402897182932343</v>
+        <v>0.005402897182932325</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004557573482352537</v>
+        <v>0.004557573482352515</v>
       </c>
       <c r="M2" t="n">
         <v>0.01141417043866515</v>
       </c>
       <c r="N2" t="n">
-        <v>0.003892716356798823</v>
+        <v>0.003892716356798803</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00253611456942409</v>
+        <v>0.002536114569424077</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001849133738923396</v>
+        <v>0.001849133738923381</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00197501920318733</v>
+        <v>0.001975019203187321</v>
       </c>
       <c r="R2" t="n">
-        <v>0.002037516731428112</v>
+        <v>0.002037516731428099</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003045065014439775</v>
+        <v>0.003045065014439763</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003655110577941481</v>
+        <v>0.003655110577941467</v>
       </c>
       <c r="U2" t="n">
-        <v>0.007338056659135384</v>
+        <v>0.007338056659135373</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001501587635041709</v>
+        <v>0.001501587635041708</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004425996524983936</v>
+        <v>0.004425996524983922</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004791804445048409</v>
+        <v>0.004791804445048388</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.006358203971473563</v>
+        <v>0.006358203971473553</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001856054814659136</v>
+        <v>0.001856054814659127</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0044907962331658</v>
+        <v>0.004490796233165777</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0104009490766341</v>
+        <v>0.01040094907663409</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0003413574479209694</v>
+        <v>0.0003413574479209913</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004929800235832376</v>
+        <v>0.0004929800235832375</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004933358053259829</v>
+        <v>0.0004933358053259591</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004023861575616915</v>
+        <v>0.0004023861575616912</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0003616719734332827</v>
+        <v>0.0003616719734332824</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005248495077804775</v>
+        <v>0.0005248495077804648</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0004933358053259829</v>
+        <v>0.0004933358053259591</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004933358053259829</v>
+        <v>0.0004933358053259591</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004900171785819064</v>
+        <v>0.0004900171785818924</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004933358053259829</v>
+        <v>0.0004933358053259591</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004933358053259829</v>
+        <v>0.0004933358053259591</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0005139034857667771</v>
+        <v>0.0005139034857667769</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0003755271529105948</v>
+        <v>0.0003755271529105983</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0004079019935073696</v>
+        <v>0.0004079019935073214</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003999661377915087</v>
+        <v>0.0003999661377914835</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0003114902319556395</v>
+        <v>0.0003114902319556245</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0004933358053259829</v>
+        <v>0.0004933358053259591</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004933358053259829</v>
+        <v>0.0004933358053259591</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0004933358053259829</v>
+        <v>0.0004933358053259591</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0004191349447623822</v>
+        <v>0.0004191349447624174</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0004409376524858545</v>
+        <v>0.0004409376524858546</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0004933656734230818</v>
+        <v>0.0004933656734230624</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0003254193503943903</v>
+        <v>0.0003254193503943996</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.000644406358871023</v>
+        <v>0.0006444063588710234</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0003385343719068782</v>
+        <v>0.0003385343719068706</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0004933358053259829</v>
+        <v>0.0004933358053259591</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0006766268244059238</v>
+        <v>0.0006766268244059241</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004090022558678554</v>
+        <v>0.004090022558678541</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003127422264376041</v>
+        <v>0.003127422264376028</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004180779312175071</v>
+        <v>0.004180779312175049</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003350149405080996</v>
+        <v>0.003350149405080985</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003634786009313791</v>
+        <v>0.003634786009313781</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003647179951000381</v>
+        <v>0.00364717995100036</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003743337632399248</v>
+        <v>0.003743337632399228</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004178124347627955</v>
+        <v>0.004178124347627929</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003885307451146218</v>
+        <v>0.003885307451146216</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004803102647301724</v>
+        <v>0.004803102647301701</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004494992084732433</v>
+        <v>0.004494992084732406</v>
       </c>
       <c r="M4" t="n">
-        <v>0.007007212163519965</v>
+        <v>0.007007212163519952</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004252659469614647</v>
+        <v>0.00425265946961467</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00375819404813901</v>
+        <v>0.003758194048138989</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003507797602357701</v>
+        <v>0.003507797602357679</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003553681375860152</v>
+        <v>0.00355368137586013</v>
       </c>
       <c r="R4" t="n">
-        <v>0.003576460991020884</v>
+        <v>0.003576460991020864</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003943700508949363</v>
+        <v>0.003943700508949344</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004166054953329056</v>
+        <v>0.004166054953329036</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005508445552587889</v>
+        <v>0.005508445552587868</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00264409546192396</v>
+        <v>0.002644095461923958</v>
       </c>
       <c r="W4" t="n">
-        <v>0.004447033828826218</v>
+        <v>0.004447033828826199</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004580366520156247</v>
+        <v>0.004580366520156212</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.005151300753946328</v>
+        <v>0.005151300753946274</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.003510320253192004</v>
+        <v>0.003510320253191981</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004470652561541916</v>
+        <v>0.004470652561541891</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.00664042737106307</v>
+        <v>0.006640427371063063</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002958230849490423</v>
+        <v>0.0029582308494904</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003013269394401827</v>
+        <v>0.003013269394401817</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003013625176144574</v>
+        <v>0.00301362517614458</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002974103675703768</v>
+        <v>0.002974103675703756</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002963498711813493</v>
+        <v>0.002963498711813482</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003025111550636663</v>
+        <v>0.003025111550636635</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003013625176144574</v>
+        <v>0.00301362517614458</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003013625176144574</v>
+        <v>0.00301362517614458</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002900868980700578</v>
+        <v>0.002900868980700586</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003013625176144574</v>
+        <v>0.00301362517614458</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003013625176144574</v>
+        <v>0.00301362517614458</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003034192856585371</v>
+        <v>0.003034192856585359</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002970685305718205</v>
+        <v>0.002970685305718167</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00298248555495116</v>
+        <v>0.002982485554951127</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002979593028730252</v>
+        <v>0.002979593028730218</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002947344599989617</v>
+        <v>0.002947344599989628</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003013625176144574</v>
+        <v>0.00301362517614458</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003013625176144574</v>
+        <v>0.00301362517614458</v>
       </c>
       <c r="T5" t="n">
-        <v>0.003013625176144574</v>
+        <v>0.00301362517614458</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002986579833779637</v>
+        <v>0.002986579833779624</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002257500998063261</v>
+        <v>0.00225750099806326</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003013636062715238</v>
+        <v>0.003013636062715231</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002952421600096573</v>
+        <v>0.00295242160009653</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.00306868861895174</v>
+        <v>0.003068688618951713</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00295720187143352</v>
+        <v>0.002957201871433509</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003013625176144574</v>
+        <v>0.00301362517614458</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00309602609888293</v>
+        <v>0.003096026098882919</v>
       </c>
     </row>
     <row r="6">
@@ -938,82 +938,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00133138147196767</v>
+        <v>0.001331381471967665</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003687811776651578</v>
+        <v>0.0003687811776651581</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001422138225464185</v>
+        <v>0.001422138225464174</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0005915083183701124</v>
+        <v>0.0005915083183701118</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008761449226029039</v>
+        <v>0.0008761449226029042</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000878298698197885</v>
+        <v>0.0008782986981978747</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000984696545688363</v>
+        <v>0.0009846965456883517</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001419483260917066</v>
+        <v>0.001419483260917052</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001226280746543165</v>
+        <v>0.001226280746543154</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002044461560590834</v>
+        <v>0.002044461560590825</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001736350998021542</v>
+        <v>0.001736350998021535</v>
       </c>
       <c r="M6" t="n">
-        <v>0.004248571076809064</v>
+        <v>0.004248571076809068</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001494018382903753</v>
+        <v>0.001494018382903787</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0009893127953365106</v>
+        <v>0.0009893127953365022</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0007389163495552033</v>
+        <v>0.0007389163495551938</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0007950402891492655</v>
+        <v>0.0007950402891492566</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0008178199043100007</v>
+        <v>0.0008178199043099891</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001185059422238482</v>
+        <v>0.001185059422238472</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001407413866618174</v>
+        <v>0.001407413866618164</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002739564299785391</v>
+        <v>0.002739564299785384</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0006060028486443149</v>
+        <v>0.0006060028486443139</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001678152576023722</v>
+        <v>0.001678152576023714</v>
       </c>
       <c r="X6" t="n">
-        <v>0.00181148526735375</v>
+        <v>0.001811485267353728</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002392659667235438</v>
+        <v>0.002392659667235396</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0007516791664811186</v>
+        <v>0.0007516791664811084</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.00171201147483103</v>
+        <v>0.001712011474831021</v>
       </c>
       <c r="AB6" t="n">
         <v>0.003881786284352198</v>
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001995897627795378</v>
+        <v>0.0001995897627795288</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002546283076909452</v>
+        <v>0.0002546283076909451</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002549840894336911</v>
+        <v>0.0002549840894337052</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002154625889928852</v>
+        <v>0.000215462588992885</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0002048576251026071</v>
+        <v>0.0002048576251026069</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002562302978341632</v>
+        <v>0.0002562302978341478</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002549840894336911</v>
+        <v>0.0002549840894337052</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002549840894336911</v>
+        <v>0.0002549840894337052</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000241842276097527</v>
+        <v>0.0002418422760975335</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002549840894336911</v>
+        <v>0.0002549840894337052</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002549840894336911</v>
+        <v>0.0002549840894337052</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002755517698744861</v>
+        <v>0.0002755517698744858</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0002120442190073224</v>
+        <v>0.000212044219007296</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0002136043021486611</v>
+        <v>0.0002136043021486372</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0002107117759277524</v>
+        <v>0.0002107117759277288</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001887035132787316</v>
+        <v>0.0001887035132787517</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0002549840894336911</v>
+        <v>0.0002549840894337052</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002549840894336911</v>
+        <v>0.0002549840894337052</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0002549840894336911</v>
+        <v>0.0002549840894337052</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0002176985809771401</v>
+        <v>0.0002176985809771373</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0002194083847836156</v>
+        <v>0.0002194083847836154</v>
       </c>
       <c r="W7" t="n">
-        <v>0.000244754809912741</v>
+        <v>0.0002447548099127459</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0001835403472940761</v>
+        <v>0.0001835403472940424</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0003100475322408548</v>
+        <v>0.0003100475322408389</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001985607847226337</v>
+        <v>0.0001985607847226346</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0002549840894336911</v>
+        <v>0.0002549840894337052</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0003373850121720432</v>
+        <v>0.0003373850121720431</v>
       </c>
     </row>
   </sheetData>
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0002154785256680835</v>
+        <v>0.0002154785256680015</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002841243195887778</v>
+        <v>0.000284124319588778</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0003402412307564332</v>
+        <v>0.0003402412307563458</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003090290557406779</v>
+        <v>0.0003090290557406775</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0004135811772366206</v>
+        <v>0.00041358117723662</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0004605673388662545</v>
+        <v>0.0004605673388661867</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003808855347230519</v>
+        <v>0.0003808855347229703</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003873475837351898</v>
+        <v>0.000387347583735105</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00062685884513089</v>
+        <v>0.000626858845130859</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0005612367236528596</v>
+        <v>0.0005612367236527762</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000643961101967261</v>
+        <v>0.000643961101967139</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0004884415465212829</v>
+        <v>0.0004884415465212799</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0004318811577444576</v>
+        <v>0.0004318811577444867</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0004880006213370687</v>
+        <v>0.000488000621336966</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0004921085028168331</v>
+        <v>0.0004921085028168198</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0003220100451053369</v>
+        <v>0.0003220100451052522</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0006854579445562381</v>
+        <v>0.0006854579445561582</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0005646193137945402</v>
+        <v>0.0005646193137944656</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0003842286028198444</v>
+        <v>0.000384228602819794</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0007999088636333334</v>
+        <v>0.0007999088636332485</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0005518282253493571</v>
+        <v>0.000551828225349357</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0007055889463371007</v>
+        <v>0.0007055889463370552</v>
       </c>
       <c r="X2" t="n">
-        <v>0.008504280326162192</v>
+        <v>0.008504280326162099</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.005066417890750094</v>
+        <v>0.005066417890749998</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0005394901733820697</v>
+        <v>0.0005394901733820164</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001201340652243128</v>
+        <v>0.001201340652243045</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0003086887719580611</v>
+        <v>0.0003086887719580608</v>
       </c>
     </row>
     <row r="3">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0002761440416145673</v>
+        <v>0.0002761440416144909</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004133951914193134</v>
+        <v>0.000413395191419313</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004087442576888212</v>
+        <v>0.000408744257688811</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003337103398906369</v>
+        <v>0.000333710339890637</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0002946805728756716</v>
+        <v>0.0002946805728756707</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004362397763020621</v>
+        <v>0.0004362397763020452</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0004087442576888212</v>
+        <v>0.000408744257688811</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004087442576888212</v>
+        <v>0.000408744257688811</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004068263284885588</v>
+        <v>0.0004068263284885156</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004087442576888212</v>
+        <v>0.000408744257688811</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004087442576888212</v>
+        <v>0.000408744257688811</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004060395443174711</v>
+        <v>0.0004060395443174713</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0003059569066990683</v>
+        <v>0.0003059569066990147</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000334203763240306</v>
+        <v>0.0003342037632402389</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003272797761621237</v>
+        <v>0.0003272797761620336</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002500850727030039</v>
+        <v>0.0002500850727029878</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0004087442576888212</v>
+        <v>0.000408744257688811</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004087442576888212</v>
+        <v>0.000408744257688811</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0004087442576888212</v>
+        <v>0.000408744257688811</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0003439475926191313</v>
+        <v>0.0003439475926191016</v>
       </c>
       <c r="V3" t="n">
-        <v>0.000367889957217329</v>
+        <v>0.0003678899572173286</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0004087703174335565</v>
+        <v>0.0004087703174335294</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0002622381459886963</v>
+        <v>0.0002622381459886073</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.000540455159601897</v>
+        <v>0.0005404551596018672</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0002736809245237122</v>
+        <v>0.0002736809245236492</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0004087442576888212</v>
+        <v>0.000408744257688811</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0005440138675431587</v>
+        <v>0.0005440138675431585</v>
       </c>
     </row>
     <row r="4">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002726603365667934</v>
+        <v>0.00272660336566784</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002754579674472085</v>
+        <v>0.002754579674472108</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002772077906634984</v>
+        <v>0.00277207790663487</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002757887253230884</v>
+        <v>0.002757887253230899</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002797461514756277</v>
+        <v>0.002797461514756289</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002815935360100517</v>
+        <v>0.002815935360100396</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002786892278161306</v>
+        <v>0.002786892278161215</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00278924761914502</v>
+        <v>0.002789247619144928</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002765409273719771</v>
+        <v>0.002765409273719772</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002852628168735639</v>
+        <v>0.002852628168735547</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002882780233232502</v>
+        <v>0.002882780233232427</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002824376304367398</v>
+        <v>0.002824376304367407</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002805479583931746</v>
+        <v>0.002805479583931715</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002825934469423265</v>
+        <v>0.002825934469423176</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002827431743985406</v>
+        <v>0.00282743174398539</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002765432853546557</v>
+        <v>0.002765432853546461</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0028979053450757</v>
+        <v>0.002897905345075606</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002853861083121891</v>
+        <v>0.002853861083121814</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002788110787226242</v>
+        <v>0.00278811078722622</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002939621361128757</v>
+        <v>0.002939621361128662</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002112972632140315</v>
+        <v>0.002112972632140317</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002905242858834665</v>
+        <v>0.002905242858834588</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005747774289923214</v>
+        <v>0.005747774289923123</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.004494713801634376</v>
+        <v>0.004494713801634296</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002844701806522786</v>
+        <v>0.002844701806522739</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003085938534226933</v>
+        <v>0.00308593853422689</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002758516820292902</v>
+        <v>0.002758516820292909</v>
       </c>
     </row>
     <row r="5">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002748715233859903</v>
+        <v>0.002748715233859889</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002801697389279119</v>
+        <v>0.002801697389279123</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002797046455548625</v>
+        <v>0.002797046455548623</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002766883291481297</v>
+        <v>0.002766883291481286</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002754123640668095</v>
+        <v>0.002754123640668113</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00280706824921449</v>
+        <v>0.002807068249214468</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002797046455548625</v>
+        <v>0.002797046455548623</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002797046455548625</v>
+        <v>0.002797046455548623</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002685210005155895</v>
+        <v>0.00268521000515589</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002797046455548625</v>
+        <v>0.002797046455548623</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002797046455548625</v>
+        <v>0.002797046455548623</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002794341742177287</v>
+        <v>0.002794341742177277</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002759581673102872</v>
+        <v>0.002759581673102855</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002769877320620836</v>
+        <v>0.002769877320620798</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002767353608636433</v>
+        <v>0.002767353608636347</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002739217045691521</v>
+        <v>0.002739217045691504</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002797046455548625</v>
+        <v>0.002797046455548623</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002797046455548625</v>
+        <v>0.002797046455548623</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002797046455548625</v>
+        <v>0.002797046455548623</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002773428832011595</v>
+        <v>0.002773428832011566</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002045929293318387</v>
+        <v>0.002045929293318388</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002797055954019607</v>
+        <v>0.002797055954019562</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002743646698195582</v>
+        <v>0.002743646698195516</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002845053532668478</v>
+        <v>0.002845053532668439</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002747817456603679</v>
+        <v>0.002747817456603653</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002797046455548625</v>
+        <v>0.002797046455548623</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00284429005430687</v>
+        <v>0.002844290054306892</v>
       </c>
     </row>
     <row r="6">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000130988810547232</v>
+        <v>0.0001309888105471297</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001589651193514153</v>
+        <v>0.0001589651193514154</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001764633515142864</v>
+        <v>0.0001764633515141983</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001622726981102023</v>
+        <v>0.0001622726981102024</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002018469596355973</v>
+        <v>0.0002018469596355971</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0002107382185889985</v>
+        <v>0.0002107382185888841</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001912777230406047</v>
+        <v>0.0001912777230405058</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000193633064024317</v>
+        <v>0.0001936330640242136</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002705081897391808</v>
+        <v>0.0002705081897391563</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002570136136149378</v>
+        <v>0.0002570136136148356</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002871656781118141</v>
+        <v>0.0002871656781117773</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0002287617492467104</v>
+        <v>0.000228761749246708</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0002098650288110706</v>
+        <v>0.0002098650288110077</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0002207373279117421</v>
+        <v>0.0002207373279116596</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0002222346024738782</v>
+        <v>0.0002222346024738763</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001698182984258515</v>
+        <v>0.0001698182984257511</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003022907899549974</v>
+        <v>0.0003022907899548754</v>
       </c>
       <c r="S6" t="n">
-        <v>0.000258246528001204</v>
+        <v>0.0002582465280010996</v>
       </c>
       <c r="T6" t="n">
-        <v>0.000192496232105544</v>
+        <v>0.0001924962321055069</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0003344242196172317</v>
+        <v>0.0003344242196171445</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002416995042004317</v>
+        <v>0.0002416995042004318</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0003000457173231412</v>
+        <v>0.0003000457173230673</v>
       </c>
       <c r="X6" t="n">
-        <v>0.003142577148411683</v>
+        <v>0.003142577148411595</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001899099246513682</v>
+        <v>0.001899099246513589</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0002490872514020769</v>
+        <v>0.0002490872514020313</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0004903239791062236</v>
+        <v>0.0004903239791062061</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0001629022651722157</v>
+        <v>0.0001629022651722155</v>
       </c>
     </row>
     <row r="7">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001531006787392086</v>
+        <v>0.0001531006787391647</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002060828341584291</v>
+        <v>0.0002060828341584292</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002014319004279328</v>
+        <v>0.0002014319004279115</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001712687363605918</v>
+        <v>0.0001712687363605917</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001585090855474186</v>
+        <v>0.0001585090855474184</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002018711077029784</v>
+        <v>0.000201871107702949</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002014319004279328</v>
+        <v>0.0002014319004279115</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002014319004279328</v>
+        <v>0.0002014319004279115</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001903089211753174</v>
+        <v>0.000190308921175279</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002014319004279328</v>
+        <v>0.0002014319004279115</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002014319004279328</v>
+        <v>0.0002014319004279115</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0001987271870565839</v>
+        <v>0.0001987271870565825</v>
       </c>
       <c r="N7" t="n">
-        <v>0.000163967117982204</v>
+        <v>0.0001639671179821436</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001646801791093106</v>
+        <v>0.0001646801791092769</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001621564671249213</v>
+        <v>0.0001621564671248349</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001436024905708373</v>
+        <v>0.0001436024905707918</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0002014319004279328</v>
+        <v>0.0002014319004279115</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002014319004279328</v>
+        <v>0.0002014319004279115</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0002014319004279328</v>
+        <v>0.0002014319004279115</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001682316905000752</v>
+        <v>0.0001682316905000544</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001746561653785014</v>
+        <v>0.0001746561653785013</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001918588125080894</v>
+        <v>0.0001918588125080467</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0001384495566840786</v>
+        <v>0.0001384495566840037</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0002494389775477816</v>
+        <v>0.0002494389775477219</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001522029014829936</v>
+        <v>0.0001522029014829422</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0002014319004279328</v>
+        <v>0.0002014319004279115</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0002486754991861976</v>
+        <v>0.0002486754991861971</v>
       </c>
     </row>
   </sheetData>
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0027631899848477</v>
+        <v>0.002763189984847757</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007376632026081691</v>
+        <v>0.0007376632026081898</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003787923532784448</v>
+        <v>0.003787923532784433</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001275606958853338</v>
+        <v>0.00127560695885339</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001376024341095191</v>
+        <v>0.001376024341095195</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002113089583067536</v>
+        <v>0.002113089583067523</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008601058107077567</v>
+        <v>0.0008601058107077518</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002018120883573827</v>
+        <v>0.002018120883573819</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003029790844097162</v>
+        <v>0.003029790844097136</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004689077011244281</v>
+        <v>0.004689077011244279</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004211781787618318</v>
+        <v>0.004211781787618599</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01053657892247563</v>
+        <v>0.01053657892247562</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002375266936149738</v>
+        <v>0.002375266936149733</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001973360851756251</v>
+        <v>0.001973360851756248</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002027277219550689</v>
+        <v>0.002027277219550693</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001393858036343402</v>
+        <v>0.001393858036343397</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0009417545656309387</v>
+        <v>0.000941754565630932</v>
       </c>
       <c r="S2" t="n">
-        <v>0.002978844511469019</v>
+        <v>0.002978844511469039</v>
       </c>
       <c r="T2" t="n">
-        <v>0.002688097940537455</v>
+        <v>0.002688097940537453</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006663705899884669</v>
+        <v>0.006663705899884658</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0009699599623562067</v>
+        <v>0.0009699599623561971</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004047391705231215</v>
+        <v>0.004047391705231212</v>
       </c>
       <c r="X2" t="n">
-        <v>0.005709309156838941</v>
+        <v>0.005709309156838921</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.005574010596756907</v>
+        <v>0.005574010596756903</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0015300959415441</v>
+        <v>0.00153009594154411</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003401380816890489</v>
+        <v>0.003401380816890504</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.009988223899676851</v>
+        <v>0.009988223899676905</v>
       </c>
     </row>
     <row r="3">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0003257161157723757</v>
+        <v>0.0003257161157723417</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004737599014799478</v>
+        <v>0.0004737599014799272</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000473016527200482</v>
+        <v>0.0004730165272004753</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003858709894143103</v>
+        <v>0.0003858709894143104</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0003439821645545463</v>
+        <v>0.0003439821645545471</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005035602270827049</v>
+        <v>0.0005035602270826909</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000473016527200482</v>
+        <v>0.0004730165272004753</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000473016527200482</v>
+        <v>0.0004730165272004753</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004699413590990689</v>
+        <v>0.0004699413590990665</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000473016527200482</v>
+        <v>0.0004730165272004753</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000473016527200482</v>
+        <v>0.0004730165272004753</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004926362983972381</v>
+        <v>0.0004926362983972394</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0003588340655206954</v>
+        <v>0.0003588340655206886</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0003902123974181155</v>
+        <v>0.0003902123974180654</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003825208100634455</v>
+        <v>0.0003825208100634305</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002967682229601525</v>
+        <v>0.0002967682229601193</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000473016527200482</v>
+        <v>0.0004730165272004753</v>
       </c>
       <c r="S3" t="n">
-        <v>0.000473016527200482</v>
+        <v>0.0004730165272004753</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000473016527200482</v>
+        <v>0.0004730165272004753</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0004010923828143437</v>
+        <v>0.0004010923828143125</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0004225753973069488</v>
+        <v>0.0004225753973069606</v>
       </c>
       <c r="W3" t="n">
-        <v>0.000473045475948029</v>
+        <v>0.0004730454759480219</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00031026859835547</v>
+        <v>0.0003102685983554583</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0006194247400502734</v>
+        <v>0.0006194247400502376</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0003229799350063679</v>
+        <v>0.0003229799350063369</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.000473016527200482</v>
+        <v>0.0004730165272004753</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0006515338653445446</v>
+        <v>0.0006515338653445443</v>
       </c>
     </row>
     <row r="4">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003807426895391205</v>
+        <v>0.003807426895391198</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00306961859128497</v>
+        <v>0.003069618591284957</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004180930240585312</v>
+        <v>0.004180930240585295</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003259683509227024</v>
+        <v>0.003259683509227027</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003298846073922058</v>
+        <v>0.00329884607392205</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003570472932806675</v>
+        <v>0.003570472932806665</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003113775061059831</v>
+        <v>0.003113775061059821</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003535857957019991</v>
+        <v>0.003535857957019974</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003769073671509659</v>
+        <v>0.003769073671509636</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004509390101605519</v>
+        <v>0.004509390101605512</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004335421597277343</v>
+        <v>0.004335421597277362</v>
       </c>
       <c r="M4" t="n">
-        <v>0.006653204478397678</v>
+        <v>0.006653204478397674</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003666033499363229</v>
+        <v>0.003666033499363227</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003519543451021315</v>
+        <v>0.003519543451021301</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003539195333964435</v>
+        <v>0.003539195333964422</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003308321479668952</v>
+        <v>0.003308321479668949</v>
       </c>
       <c r="R4" t="n">
-        <v>0.003143535073461246</v>
+        <v>0.00314353507346123</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003886030438001376</v>
+        <v>0.003886030438001366</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003780056727015428</v>
+        <v>0.003780056727015415</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005229119144251853</v>
+        <v>0.005229119144251843</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002256208180712519</v>
+        <v>0.00225620818071254</v>
       </c>
       <c r="W4" t="n">
-        <v>0.004275503342613052</v>
+        <v>0.004275503342613042</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004881252738504073</v>
+        <v>0.004881252738504083</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.004831938002110073</v>
+        <v>0.004831938002110065</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00335797859632836</v>
+        <v>0.003357978596328336</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004040039959655698</v>
+        <v>0.004040039959655696</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.006456532116795284</v>
+        <v>0.006456532116795289</v>
       </c>
     </row>
     <row r="5">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0029189962923765</v>
+        <v>0.002918996292376489</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002973428936932755</v>
+        <v>0.002973428936932704</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002972685562653286</v>
+        <v>0.002972685562653242</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002935385196173739</v>
+        <v>0.002935385196173733</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002922678819424089</v>
+        <v>0.00292267881942408</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002983818382598126</v>
+        <v>0.002983818382598096</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002972685562653286</v>
+        <v>0.002972685562653242</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002972685562653286</v>
+        <v>0.002972685562653242</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002836038593498136</v>
+        <v>0.002836038593498123</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002972685562653286</v>
+        <v>0.002972685562653242</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002972685562653286</v>
+        <v>0.002972685562653242</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002992305333850028</v>
+        <v>0.002992305333850013</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002931067396169162</v>
+        <v>0.002931067396169143</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002942504429682794</v>
+        <v>0.002942504429682771</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002939700936411201</v>
+        <v>0.002939700936411167</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002908445125369765</v>
+        <v>0.002908445125369755</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002972685562653286</v>
+        <v>0.002972685562653242</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002972685562653286</v>
+        <v>0.002972685562653242</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002972685562653286</v>
+        <v>0.002972685562653242</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002946470056600482</v>
+        <v>0.002946470056600454</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002056692934466151</v>
+        <v>0.002056692934466149</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002972696114131835</v>
+        <v>0.002972696114131819</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002913365853671946</v>
+        <v>0.002913365853671938</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003026049637025003</v>
+        <v>0.003026049637024961</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00291799898661715</v>
+        <v>0.002917998986617129</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002972685562653286</v>
+        <v>0.002972685562653242</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003053418236230863</v>
+        <v>0.00305341823623086</v>
       </c>
     </row>
     <row r="6">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001076829275817515</v>
+        <v>0.001076829275817511</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0003390209717112755</v>
+        <v>0.0003390209717112766</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001450332621011617</v>
+        <v>0.001450332621011589</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0005290858896533285</v>
+        <v>0.000529085889653343</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0005682484543483656</v>
+        <v>0.0005682484543483683</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0008298637587763604</v>
+        <v>0.0008298637587763498</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003831774414861366</v>
+        <v>0.000383177441486109</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008052603374462956</v>
+        <v>0.000805260337446268</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001162436104138914</v>
+        <v>0.001162436104138899</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001778792482031824</v>
+        <v>0.0017787924820318</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001604823977703648</v>
+        <v>0.001604823977703637</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003922606858823988</v>
+        <v>0.003922606858823982</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0009354358797895308</v>
+        <v>0.0009354358797895066</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0007789342769910006</v>
+        <v>0.0007789342769909931</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0007985861599341206</v>
+        <v>0.0007985861599341146</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0005777238600952554</v>
+        <v>0.0005777238600952287</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0004129374538875505</v>
+        <v>0.0004129374538875219</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00115543281842768</v>
+        <v>0.001155432818427657</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001049459107441733</v>
+        <v>0.001049459107441709</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002488509970221538</v>
+        <v>0.002488509970221534</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0004073709493370277</v>
+        <v>0.0004073709493370136</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001534894168582738</v>
+        <v>0.001534894168582734</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002140643564473756</v>
+        <v>0.002140643564473763</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002101340382536379</v>
+        <v>0.002101340382536353</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0006273809767546576</v>
+        <v>0.0006273809767546598</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001309442340082002</v>
+        <v>0.001309442340081983</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003725934497221594</v>
+        <v>0.003725934497221602</v>
       </c>
     </row>
     <row r="7">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001883986728028061</v>
+        <v>0.0001883986728027702</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002428313173590575</v>
+        <v>0.0002428313173589906</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002420879430795919</v>
+        <v>0.0002420879430795793</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002047875766000434</v>
+        <v>0.0002047875766000439</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001920811998503924</v>
+        <v>0.0001920811998503934</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002432092085678101</v>
+        <v>0.0002432092085677915</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002420879430795919</v>
+        <v>0.0002420879430795795</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002420879430795919</v>
+        <v>0.0002420879430795795</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00022940102612739</v>
+        <v>0.0002294010261273792</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002420879430795919</v>
+        <v>0.0002420879430795793</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002420879430795919</v>
+        <v>0.0002420879430795795</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002617077142763329</v>
+        <v>0.0002617077142763346</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0002004697765954679</v>
+        <v>0.0002004697765954393</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0002018952556524837</v>
+        <v>0.0002018952556524559</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001990917623808851</v>
+        <v>0.0001990917623808584</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001778475057960698</v>
+        <v>0.0001778475057960297</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0002420879430795919</v>
+        <v>0.0002420879430795795</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002420879430795919</v>
+        <v>0.0002420879430795793</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0002420879430795919</v>
+        <v>0.0002420879430795795</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0002058608825701689</v>
+        <v>0.0002058608825701535</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0002078557030906579</v>
+        <v>0.000207855703090671</v>
       </c>
       <c r="W7" t="n">
-        <v>0.000232086940101519</v>
+        <v>0.0002320869401015146</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0001727566796416337</v>
+        <v>0.0001727566796416348</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0002954520174513056</v>
+        <v>0.0002954520174512816</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001874013670434542</v>
+        <v>0.00018740136704343</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0002420879430795919</v>
+        <v>0.0002420879430795793</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.00032282061665717</v>
+        <v>0.0003228206166571705</v>
       </c>
     </row>
   </sheetData>
@@ -2641,82 +2641,82 @@
         <v>0.002179858807583377</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0005752077033218519</v>
+        <v>0.000575207703321852</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004369877748135696</v>
+        <v>0.004369877748135691</v>
       </c>
       <c r="E2" t="n">
         <v>0.00127209614007666</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001351489888327542</v>
+        <v>0.001351489888327544</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00197117006557457</v>
+        <v>0.001971170065574565</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003889461978192096</v>
+        <v>0.0003889461978192068</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002731656470141888</v>
+        <v>0.002731656470141879</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002997437551020659</v>
+        <v>0.002997437551020657</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003754446481470807</v>
+        <v>0.003754446481470803</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003556669795775817</v>
+        <v>0.003556669795775805</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009118977750020768</v>
+        <v>0.009118977750020766</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00162119023840543</v>
+        <v>0.00162119023840542</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001514441081269154</v>
+        <v>0.001514441081269145</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001854020260094389</v>
+        <v>0.001854020260094375</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001184038218834904</v>
+        <v>0.001184038218834903</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0005121749641096939</v>
+        <v>0.0005121749641096872</v>
       </c>
       <c r="S2" t="n">
-        <v>0.002721087887970455</v>
+        <v>0.002721087887970446</v>
       </c>
       <c r="T2" t="n">
-        <v>0.002430377416517311</v>
+        <v>0.002430377416517306</v>
       </c>
       <c r="U2" t="n">
-        <v>0.005836166231380635</v>
+        <v>0.00583616623138062</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001188644824224031</v>
+        <v>0.001188644824224044</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003647722130577074</v>
+        <v>0.003647722130577057</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01102550642566584</v>
+        <v>0.01102550642566583</v>
       </c>
       <c r="Y2" t="n">
         <v>0.01098519567936325</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001511330441467804</v>
+        <v>0.001511330441467795</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003455461356096833</v>
+        <v>0.003455461356096823</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.009366046653369792</v>
+        <v>0.009366046653369729</v>
       </c>
     </row>
     <row r="3">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0003219307081630072</v>
+        <v>0.0003219307081630091</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004680703896404527</v>
+        <v>0.000468070389640453</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004676040124808486</v>
+        <v>0.0004676040124808498</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000381583164667995</v>
+        <v>0.0003815831646679953</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0003400689796492895</v>
+        <v>0.0003400689796492897</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004978103211042312</v>
+        <v>0.0004978103211042334</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0004676040124808486</v>
+        <v>0.0004676040124808498</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004676040124808486</v>
+        <v>0.0004676040124808498</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000464611407417984</v>
+        <v>0.0004646114074179975</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004676040124808486</v>
+        <v>0.0004676040124808498</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004676040124808486</v>
+        <v>0.0004676040124808498</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004834915824305055</v>
+        <v>0.0004834915824305054</v>
       </c>
       <c r="N3" t="n">
-        <v>0.000354682831020898</v>
+        <v>0.0003546828310209006</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0003857145521629717</v>
+        <v>0.0003857145521629892</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003781079274796574</v>
+        <v>0.0003781079274796611</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002933025790345574</v>
+        <v>0.0002933025790345741</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0004676040124808486</v>
+        <v>0.0004676040124808498</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004676040124808486</v>
+        <v>0.0004676040124808498</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0004676040124808486</v>
+        <v>0.0004676040124808498</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0003964356732612583</v>
+        <v>0.0003964356732612943</v>
       </c>
       <c r="V3" t="n">
-        <v>0.000418231355096807</v>
+        <v>0.0004182313550968205</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0004676326414563669</v>
+        <v>0.000467632641456376</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0003066538268308548</v>
+        <v>0.0003066538268308654</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0006123287999570477</v>
+        <v>0.0006123287999570312</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0003192247517468523</v>
+        <v>0.0003192247517468512</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0004676040124808486</v>
+        <v>0.0004676040124808498</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0006424663473308482</v>
+        <v>0.0006424663473308305</v>
       </c>
     </row>
     <row r="4">
@@ -2814,85 +2814,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003587799987898512</v>
+        <v>0.003587799987898506</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003003219891321189</v>
+        <v>0.003003219891321193</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004386036175229062</v>
+        <v>0.004386036175229055</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003251558468674107</v>
+        <v>0.003251558468674113</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003282973899044929</v>
+        <v>0.003282973899044936</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003511735391983235</v>
+        <v>0.003511735391983229</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002935033371597092</v>
+        <v>0.002935033371597085</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003788923756365796</v>
+        <v>0.003788923756365789</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003758940408631403</v>
+        <v>0.003758940408631415</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004161718705288503</v>
+        <v>0.004161718705288495</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00408963142576378</v>
+        <v>0.004089631425763772</v>
       </c>
       <c r="M4" t="n">
-        <v>0.006127124096432639</v>
+        <v>0.006127124096432634</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003384171854650703</v>
+        <v>0.003384171854650694</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003345263040386413</v>
+        <v>0.003345263040386403</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00346903566352817</v>
+        <v>0.003469035663528163</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003224835076815424</v>
+        <v>0.003224835076815423</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002979948809884741</v>
+        <v>0.002979948809884737</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003785071632266861</v>
+        <v>0.003785071632266851</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003679111079116898</v>
+        <v>0.003679111079116895</v>
       </c>
       <c r="U4" t="n">
-        <v>0.004920481109343157</v>
+        <v>0.00492048110934315</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002386815151010565</v>
+        <v>0.002386815151010606</v>
       </c>
       <c r="W4" t="n">
-        <v>0.004122818932608339</v>
+        <v>0.004122818932608329</v>
       </c>
       <c r="X4" t="n">
-        <v>0.006811934673851021</v>
+        <v>0.00681193467385101</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.006797241880176413</v>
+        <v>0.006797241880176399</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.003344129248705806</v>
+        <v>0.003344129248705797</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004052742137950292</v>
+        <v>0.004052742137950283</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.006221503622949849</v>
+        <v>0.006221503622949767</v>
       </c>
     </row>
     <row r="5">
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002910607012553017</v>
+        <v>0.002910607012553015</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002964169598554172</v>
+        <v>0.002964169598554173</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002963703221394563</v>
+        <v>0.002963703221394579</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002926976946068959</v>
+        <v>0.002926976946068958</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002914322854535644</v>
+        <v>0.002914322854535651</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002974713066187404</v>
+        <v>0.002974713066187425</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002963703221394563</v>
+        <v>0.002963703221394579</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002963703221394563</v>
+        <v>0.002963703221394579</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002835755021234419</v>
+        <v>0.00283575502123443</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002963703221394563</v>
+        <v>0.002963703221394579</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002963703221394563</v>
+        <v>0.002963703221394579</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002979590791344184</v>
+        <v>0.002979590791344189</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002922544776739875</v>
+        <v>0.002922544776739889</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002933855474703296</v>
+        <v>0.002933855474703308</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002931082949327721</v>
+        <v>0.002931082949327714</v>
       </c>
       <c r="Q5" t="n">
         <v>0.002900172395654161</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002963703221394563</v>
+        <v>0.002963703221394579</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002963703221394563</v>
+        <v>0.002963703221394579</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002963703221394563</v>
+        <v>0.002963703221394579</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002937763197449855</v>
+        <v>0.002937763197449867</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002106008488165394</v>
+        <v>0.002106008488165387</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002963713656319965</v>
+        <v>0.00296371365631998</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002905038768697651</v>
+        <v>0.002905038768697668</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003016453706985385</v>
+        <v>0.003016453706985379</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002909620723214275</v>
+        <v>0.002909620723214273</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002963703221394563</v>
+        <v>0.002963703221394579</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003041861038850477</v>
+        <v>0.003041861038850399</v>
       </c>
     </row>
     <row r="6">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0008633906200019225</v>
+        <v>0.000863390620001912</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0002788105234245987</v>
+        <v>0.0002788105234245989</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001661626807332472</v>
+        <v>0.001661626807332463</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0005271491007775245</v>
+        <v>0.0005271491007775241</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0005585645311483407</v>
+        <v>0.0005585645311483417</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0007773575130432029</v>
+        <v>0.0007773575130431898</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0002106240037005067</v>
+        <v>0.0002106240037004943</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001064514388469206</v>
+        <v>0.001064514388469195</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001149911956425081</v>
+        <v>0.001149911956425094</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001437309337391914</v>
+        <v>0.001437309337391904</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001365222057867186</v>
+        <v>0.001365222057867178</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003402714728536043</v>
+        <v>0.003402714728536047</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0006597624867541099</v>
+        <v>0.0006597624867540989</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0006108851614463836</v>
+        <v>0.0006108851614463726</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0007346577845881418</v>
+        <v>0.0007346577845881285</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0005004257089188357</v>
+        <v>0.0005004257089188294</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0002555394419881564</v>
+        <v>0.000255539441988143</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001060662264370274</v>
+        <v>0.001060662264370266</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0009547017112203131</v>
+        <v>0.0009547017112203032</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002186103230403131</v>
+        <v>0.002186103230403121</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0004867107520476038</v>
+        <v>0.0004867107520476184</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001388441053668308</v>
+        <v>0.001388441053668296</v>
       </c>
       <c r="X6" t="n">
-        <v>0.004077556794910998</v>
+        <v>0.004077556794910981</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.004072832512279817</v>
+        <v>0.004072832512279808</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0006197198808092151</v>
+        <v>0.0006197198808092019</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001328332770053695</v>
+        <v>0.001328332770053684</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003497094255053187</v>
+        <v>0.003497094255053173</v>
       </c>
     </row>
     <row r="7">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001861976446564318</v>
+        <v>0.0001861976446564208</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002397602306575837</v>
+        <v>0.0002397602306575841</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002392938534979761</v>
+        <v>0.0002392938534979923</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000202567578172371</v>
+        <v>0.0002025675781723712</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001899134866390567</v>
+        <v>0.0001899134866390569</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002403351872473698</v>
+        <v>0.000240335187247389</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002392938534979761</v>
+        <v>0.0002392938534979923</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002392938534979761</v>
+        <v>0.0002392938534979923</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002267265690281007</v>
+        <v>0.0002267265690281011</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002392938534979761</v>
+        <v>0.0002392938534979923</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002392938534979761</v>
+        <v>0.0002392938534979923</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002551814234475969</v>
+        <v>0.0002551814234475971</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001981354088432843</v>
+        <v>0.0001981354088433009</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001994775957632678</v>
+        <v>0.000199477595763274</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001967050703876901</v>
+        <v>0.0001967050703876812</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001757630277575764</v>
+        <v>0.000175763027757568</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0002392938534979761</v>
+        <v>0.0002392938534979923</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002392938534979761</v>
+        <v>0.0002392938534979923</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0002392938534979761</v>
+        <v>0.0002392938534979923</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0002033853185098268</v>
+        <v>0.0002033853185098317</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0002059040892024314</v>
+        <v>0.0002059040892024364</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0002293357773799348</v>
+        <v>0.000229335777379948</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0001706608897576173</v>
+        <v>0.0001706608897576316</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0002920443390887958</v>
+        <v>0.0002920443390887838</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001852113553176839</v>
+        <v>0.0001852113553176819</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0002392938534979761</v>
+        <v>0.0002392938534979923</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0003174516709538169</v>
+        <v>0.0003174516709538092</v>
       </c>
     </row>
   </sheetData>
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001862482282518658</v>
+        <v>0.00186248228251863</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0005705205442831792</v>
+        <v>0.0005705205442831788</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003099347425288326</v>
+        <v>0.003099347425288306</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009198622209683514</v>
+        <v>0.0009198622209683512</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001527870371255463</v>
+        <v>0.001527870371255464</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001753116896327588</v>
+        <v>0.001753116896327571</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003890604557456811</v>
+        <v>0.0003890604557456514</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002720281375220557</v>
+        <v>0.002720281375220524</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002902773034223268</v>
+        <v>0.002902773034223254</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004404752215074172</v>
+        <v>0.004404752215074146</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002992089877944996</v>
+        <v>0.002992089877944977</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007549651585713571</v>
+        <v>0.007549651585713609</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001116494848745627</v>
+        <v>0.001116494848745598</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001145545327774916</v>
+        <v>0.001145545327774885</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001596551286937574</v>
+        <v>0.001596551286937556</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001196311131186806</v>
+        <v>0.001196311131186773</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0009133785923629245</v>
+        <v>0.0009133785923628947</v>
       </c>
       <c r="S2" t="n">
-        <v>0.002575972888697649</v>
+        <v>0.002575972888697628</v>
       </c>
       <c r="T2" t="n">
-        <v>0.002428119057785992</v>
+        <v>0.002428119057785967</v>
       </c>
       <c r="U2" t="n">
-        <v>0.006271676506233165</v>
+        <v>0.00627167650623313</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001778254278094307</v>
+        <v>0.0017782542780943</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003074910889475483</v>
+        <v>0.003074910889475452</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01322021920713004</v>
+        <v>0.01322021920713001</v>
       </c>
       <c r="Y2" t="n">
         <v>0.01688793096259531</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001329891141718076</v>
+        <v>0.001329891141718065</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003683416790184991</v>
+        <v>0.003683416790184961</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.008292434333207413</v>
+        <v>0.008292434333207416</v>
       </c>
     </row>
     <row r="3">
@@ -3410,85 +3410,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0003188164711152678</v>
+        <v>0.0003188164711152552</v>
       </c>
       <c r="C3" t="n">
         <v>0.0004649456071418991</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004636950633133012</v>
+        <v>0.0004636950633132723</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003783467862766235</v>
+        <v>0.000378346786276623</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000338327020321962</v>
+        <v>0.0003383270203219617</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004937365832016223</v>
+        <v>0.0004937365832015892</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0004636950633133012</v>
+        <v>0.0004636950633132723</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004636950633133012</v>
+        <v>0.0004636950633132723</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004613396484408491</v>
+        <v>0.0004613396484408468</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004636950633133012</v>
+        <v>0.0004636950633132723</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004636950633133012</v>
+        <v>0.0004636950633132723</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004760658142375322</v>
+        <v>0.0004760658142375638</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0003513899166988256</v>
+        <v>0.0003513899166988149</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0003822523461168546</v>
+        <v>0.0003822523461168216</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003746872189257201</v>
+        <v>0.0003746872189256846</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002903445210565359</v>
+        <v>0.0002903445210565242</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0004636950633133012</v>
+        <v>0.0004636950633132723</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004636950633133012</v>
+        <v>0.0004636950633132723</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0004636950633133012</v>
+        <v>0.0004636950633132723</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0003928959614316016</v>
+        <v>0.0003928959614315758</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0004165180894395207</v>
+        <v>0.000416518089439514</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0004637235361059054</v>
+        <v>0.0004637235361058829</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0003036229319084527</v>
+        <v>0.0003036229319084443</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0006075977801127106</v>
+        <v>0.0006075977801126914</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0003161252768846631</v>
+        <v>0.0003161252768846348</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0004636950633133012</v>
+        <v>0.0004636950633132723</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.000634869105531495</v>
+        <v>0.0006348691055314947</v>
       </c>
     </row>
     <row r="4">
@@ -3498,85 +3498,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003453119986968541</v>
+        <v>0.003453119986968522</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002983009839650103</v>
+        <v>0.002983009839650099</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0039039428075043</v>
+        <v>0.00390394280750428</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003104331859924765</v>
+        <v>0.003104331859924763</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00332921330885965</v>
+        <v>0.003329213308859645</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003413257587935096</v>
+        <v>0.003413257587935083</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002916075032902408</v>
+        <v>0.00291607503290239</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003765777683472885</v>
+        <v>0.003765777683472866</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003720637594353716</v>
+        <v>0.003720637594353704</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004379747524544275</v>
+        <v>0.004379747524544254</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003864848690979353</v>
+        <v>0.003864848690979344</v>
       </c>
       <c r="M4" t="n">
-        <v>0.005533888173346447</v>
+        <v>0.005533888173346474</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003181216327184986</v>
+        <v>0.003181216327184966</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00319180488566321</v>
+        <v>0.00319180488566319</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003356191261798643</v>
+        <v>0.003356191261798629</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003210308424884687</v>
+        <v>0.003210308424884665</v>
       </c>
       <c r="R4" t="n">
-        <v>0.003107182836844989</v>
+        <v>0.00310718283684497</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003713178934691096</v>
+        <v>0.003713178934691065</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003659287949511129</v>
+        <v>0.003659287949511108</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005060219506139877</v>
+        <v>0.005060219506139854</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00268270870594419</v>
+        <v>0.002682708705944213</v>
       </c>
       <c r="W4" t="n">
-        <v>0.003895035977148799</v>
+        <v>0.003895035977148781</v>
       </c>
       <c r="X4" t="n">
-        <v>0.007592881726708885</v>
+        <v>0.007592881726708875</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.008929719593130114</v>
+        <v>0.008929719593130101</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00325899677014767</v>
+        <v>0.003258996770147646</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004116829232520366</v>
+        <v>0.004116829232520347</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.00580936816738864</v>
+        <v>0.005809368167388636</v>
       </c>
     </row>
     <row r="5">
@@ -3586,85 +3586,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002890471925351148</v>
+        <v>0.002890471925351124</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002944529014785611</v>
+        <v>0.002944529014785606</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002943278470956999</v>
+        <v>0.002943278470956981</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002906955842774908</v>
+        <v>0.002906955842774903</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002895638725767645</v>
+        <v>0.002895638725767643</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002954228252190971</v>
+        <v>0.002954228252190939</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002943278470956999</v>
+        <v>0.002943278470956981</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002943278470956999</v>
+        <v>0.002943278470956981</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002830763793994266</v>
+        <v>0.002830763793994257</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002943278470956999</v>
+        <v>0.002943278470956981</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002943278470956999</v>
+        <v>0.002943278470956981</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002955649221881191</v>
+        <v>0.002955649221881218</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00290234456376965</v>
+        <v>0.00290234456376962</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002913593556887569</v>
+        <v>0.002913593556887545</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002910836156860594</v>
+        <v>0.002910836156860577</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002880094233889264</v>
+        <v>0.002880094233889232</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002943278470956999</v>
+        <v>0.002943278470956981</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002943278470956999</v>
+        <v>0.002943278470956981</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002943278470956999</v>
+        <v>0.002943278470956981</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002917473029686161</v>
+        <v>0.002917473029686129</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002186371855493158</v>
+        <v>0.002186371855493187</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002943288848955569</v>
+        <v>0.002943288848955541</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002884934058721799</v>
+        <v>0.002884934058721785</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002995729321439366</v>
+        <v>0.002995729321439352</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002889491016655684</v>
+        <v>0.002889491016655657</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002943278470956999</v>
+        <v>0.002943278470956981</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003018275561571519</v>
+        <v>0.003018275561571517</v>
       </c>
     </row>
     <row r="6">
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0007465098048447446</v>
+        <v>0.0007465098048447179</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0002763996575262985</v>
+        <v>0.0002763996575262983</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001197332625380496</v>
+        <v>0.001197332625380475</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003977216778009602</v>
+        <v>0.0003977216778009607</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0006226031267358456</v>
+        <v>0.0006226031267358451</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0006966954254954356</v>
+        <v>0.0006966954254953962</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0002094648507786154</v>
+        <v>0.0002094648507785902</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001059167501349086</v>
+        <v>0.001059167501349062</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001114625787368204</v>
+        <v>0.001114625787368194</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001673137342420478</v>
+        <v>0.001673137342420457</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001158238508855563</v>
+        <v>0.001158238508855543</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002827277991222641</v>
+        <v>0.002827277991222635</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0004746061450611875</v>
+        <v>0.0004746061450611631</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0004752427232235338</v>
+        <v>0.0004752427232235037</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0006396290993589657</v>
+        <v>0.0006396290993589404</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0005036982427608866</v>
+        <v>0.0005036982427608625</v>
       </c>
       <c r="R6" t="n">
-        <v>0.000400572654721194</v>
+        <v>0.0004005726547211686</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001006568752567305</v>
+        <v>0.001006568752567268</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0009526777673873345</v>
+        <v>0.0009526777673873083</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0023436573437002</v>
+        <v>0.002343657343700168</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0007016963999691378</v>
+        <v>0.0007016963999691339</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001178473814709125</v>
+        <v>0.001178473814709094</v>
       </c>
       <c r="X6" t="n">
-        <v>0.004876319564269193</v>
+        <v>0.004876319564269186</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.006223109411006322</v>
+        <v>0.006223109411006306</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0005523865880238724</v>
+        <v>0.0005523865880238419</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001410219050396578</v>
+        <v>0.001410219050396554</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00310275798526483</v>
+        <v>0.003102757985264831</v>
       </c>
     </row>
     <row r="7">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.000183861743227332</v>
+        <v>0.0001838617432273233</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000237918832661805</v>
+        <v>0.0002379188326618047</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002366682888332116</v>
+        <v>0.0002366682888331785</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0002003456606511025</v>
+        <v>0.0002003456606511019</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001890285436438418</v>
+        <v>0.0001890285436438414</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002376660897512622</v>
+        <v>0.0002376660897512457</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002366682888332116</v>
+        <v>0.0002366682888331785</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002366682888332116</v>
+        <v>0.0002366682888331785</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002247519870087446</v>
+        <v>0.000224751987008741</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002366682888332116</v>
+        <v>0.0002366682888331785</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002366682888332116</v>
+        <v>0.0002366682888331785</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002490390397573859</v>
+        <v>0.0002490390397573756</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001957343816458332</v>
+        <v>0.0001957343816458212</v>
       </c>
       <c r="O7" t="n">
-        <v>0.000197031394447879</v>
+        <v>0.0001970313944478541</v>
       </c>
       <c r="P7" t="n">
-        <v>0.000194273994420918</v>
+        <v>0.0001942739944208934</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001734840517654516</v>
+        <v>0.0001734840517654331</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0002366682888332116</v>
+        <v>0.0002366682888331785</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002366682888332116</v>
+        <v>0.0002366682888331785</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0002366682888332116</v>
+        <v>0.0002366682888331785</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0002009108672464834</v>
+        <v>0.0002009108672464406</v>
       </c>
       <c r="V7" t="n">
-        <v>0.000205359549518105</v>
+        <v>0.0002053595495181075</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0002267266865158725</v>
+        <v>0.0002267266865158533</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0001683718962821236</v>
+        <v>0.0001683718962820985</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0002891191393155792</v>
+        <v>0.0002891191393155522</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.000182880834531888</v>
+        <v>0.0001828808345318603</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0002366682888332116</v>
+        <v>0.0002366682888331785</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.000311665379447715</v>
+        <v>0.0003116653794477147</v>
       </c>
     </row>
   </sheetData>
@@ -4006,85 +4006,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0005724059310486375</v>
+        <v>0.0005724059310486374</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000187722526417927</v>
+        <v>0.0001877225264179262</v>
       </c>
       <c r="D2" t="n">
         <v>0.001606918210356828</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000682610737524153</v>
+        <v>0.0006826107375241533</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0004257985520136288</v>
+        <v>0.000425798552013629</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007755925142785683</v>
+        <v>0.0007755925142785686</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007081116028812308</v>
+        <v>0.0007081116028812312</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009736117045480399</v>
+        <v>0.0009736117045480404</v>
       </c>
       <c r="J2" t="n">
         <v>0.001197685075680926</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002071700124212008</v>
+        <v>0.00207170012421201</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001544971375306801</v>
+        <v>0.0015449713753068</v>
       </c>
       <c r="M2" t="n">
-        <v>0.003463212267131869</v>
+        <v>0.003463212267131866</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001483642124066146</v>
+        <v>0.001483642124066144</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0005794521379443706</v>
+        <v>0.0005794521379443726</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001055642685664966</v>
+        <v>0.001055642685664967</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0008142851897406352</v>
+        <v>0.0008142851897406326</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0006513878331176681</v>
+        <v>0.0006513878331176692</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0008789006129102184</v>
+        <v>0.0008789006129102189</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007121563345429868</v>
+        <v>0.0007121563345429874</v>
       </c>
       <c r="U2" t="n">
-        <v>0.002730215582617129</v>
+        <v>0.002730215582617134</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0004633922694212016</v>
+        <v>0.0004633922694211996</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002050952159404092</v>
+        <v>0.002050952159404095</v>
       </c>
       <c r="X2" t="n">
-        <v>0.001900154791835842</v>
+        <v>0.001900154791835845</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001064599280422879</v>
+        <v>0.00106459928042288</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.000873305070472814</v>
+        <v>0.0008733050704728078</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001776821671621855</v>
+        <v>0.001776821671621854</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00994698553581252</v>
+        <v>0.009946985535812526</v>
       </c>
     </row>
     <row r="3">
@@ -4094,85 +4094,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0002889269212187793</v>
+        <v>0.0002889269212187825</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004286937476558159</v>
+        <v>0.0004286937476558156</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004256647994488646</v>
+        <v>0.0004256647994488681</v>
       </c>
       <c r="E3" t="n">
         <v>0.0003474415023937026</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0003065509192559322</v>
+        <v>0.0003065509192559314</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000454018289264213</v>
+        <v>0.0004540182892642179</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0004256647994488646</v>
+        <v>0.0004256647994488681</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004256647994488646</v>
+        <v>0.0004256647994488681</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004233904909766987</v>
+        <v>0.0004233904909766992</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004256647994488646</v>
+        <v>0.0004256647994488681</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004256647994488646</v>
+        <v>0.0004256647994488681</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004296797564170392</v>
+        <v>0.0004296797564170395</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0003196700680717468</v>
+        <v>0.0003196700680717479</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0003487983405910421</v>
+        <v>0.000348798340591044</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003416582971588052</v>
+        <v>0.0003416582971588074</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002620548072569307</v>
+        <v>0.0002620548072569311</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0004256647994488646</v>
+        <v>0.0004256647994488681</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004256647994488646</v>
+        <v>0.0004256647994488681</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0004256647994488646</v>
+        <v>0.0004256647994488681</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0003588554154097889</v>
+        <v>0.0003588554154097885</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0003817805405021455</v>
+        <v>0.0003817805405021426</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0004256916723596766</v>
+        <v>0.0004256916723596799</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0002745871054988518</v>
+        <v>0.0002745871054988521</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0005615013494851354</v>
+        <v>0.0005615013494851347</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0002863869449293565</v>
+        <v>0.0002863869449293579</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0004256647994488646</v>
+        <v>0.0004256647994488681</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0005973607639567358</v>
+        <v>0.0005973607639567339</v>
       </c>
     </row>
     <row r="4">
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002890694001247476</v>
+        <v>0.002890694001247477</v>
       </c>
       <c r="C4" t="n">
         <v>0.002752406349593407</v>
@@ -4191,49 +4191,49 @@
         <v>0.003267761579198811</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002927421437721101</v>
+        <v>0.0029274214377211</v>
       </c>
       <c r="F4" t="n">
         <v>0.002834919815899546</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002964753124897464</v>
+        <v>0.002964753124897462</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002940157125094006</v>
+        <v>0.002940157125094012</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003036928794491957</v>
+        <v>0.003036928794491964</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002991098907518753</v>
+        <v>0.002991098907518755</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00343716912905424</v>
+        <v>0.003437169129054242</v>
       </c>
       <c r="L4" t="n">
         <v>0.003245182685239535</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003946910517487252</v>
+        <v>0.003946910517487251</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003222828893326744</v>
+        <v>0.003222828893326745</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002893262260920233</v>
+        <v>0.002893262260920232</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003066828123852668</v>
+        <v>0.003066828123852667</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002978856150751052</v>
+        <v>0.002978856150751055</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002919481977099319</v>
+        <v>0.002919481977099321</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003002407713743763</v>
+        <v>0.003002407713743764</v>
       </c>
       <c r="T4" t="n">
         <v>0.002941631382289077</v>
@@ -4242,25 +4242,25 @@
         <v>0.003677190280963992</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002005852370988374</v>
+        <v>0.002005852370988373</v>
       </c>
       <c r="W4" t="n">
-        <v>0.003429606739516662</v>
+        <v>0.00342960673951666</v>
       </c>
       <c r="X4" t="n">
-        <v>0.003374642869790122</v>
+        <v>0.003374642869790124</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003070092697468278</v>
+        <v>0.00307009269746828</v>
       </c>
       <c r="Z4" t="n">
         <v>0.003000368204231502</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003329689395722741</v>
+        <v>0.00332968939572274</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.006325960208840323</v>
+        <v>0.00632596020884032</v>
       </c>
     </row>
     <row r="5">
@@ -4270,61 +4270,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002787369230943091</v>
+        <v>0.002787369230943097</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002840237530107677</v>
+        <v>0.002840237530107678</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002837208581900725</v>
+        <v>0.002837208581900724</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002805256187271917</v>
+        <v>0.002805256187271918</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002791455454035763</v>
+        <v>0.002791455454035762</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002847543095994932</v>
+        <v>0.002847543095994935</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002837208581900725</v>
+        <v>0.002837208581900724</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002837208581900725</v>
+        <v>0.002837208581900724</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002708877623620123</v>
+        <v>0.002708877623620122</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002837208581900725</v>
+        <v>0.002837208581900724</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002837208581900725</v>
+        <v>0.002837208581900724</v>
       </c>
       <c r="M5" t="n">
         <v>0.002841223538868893</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002798574746966739</v>
+        <v>0.00279857474696674</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002809191660258577</v>
+        <v>0.00280919166025858</v>
       </c>
       <c r="P5" t="n">
         <v>0.002806589198270153</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002777574660952288</v>
+        <v>0.00277757466095229</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002837208581900725</v>
+        <v>0.002837208581900724</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002837208581900725</v>
+        <v>0.002837208581900724</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002837208581900725</v>
+        <v>0.002837208581900724</v>
       </c>
       <c r="U5" t="n">
         <v>0.002812857345933875</v>
@@ -4336,19 +4336,19 @@
         <v>0.002837218376761157</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002782142536499796</v>
+        <v>0.002782142536499793</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002886719409315642</v>
+        <v>0.002886719409315645</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002786443439411505</v>
+        <v>0.00278644343941151</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002837208581900725</v>
+        <v>0.002837208581900724</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002918131768335967</v>
+        <v>0.002918131768335969</v>
       </c>
     </row>
     <row r="6">
@@ -4358,85 +4358,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0002652369817776331</v>
+        <v>0.0002652369817776317</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001269493301235617</v>
+        <v>0.0001269493301235612</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0006423045597289667</v>
+        <v>0.0006423045597289657</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0003019644182512551</v>
+        <v>0.0003019644182512546</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002094627964296975</v>
+        <v>0.0002094627964296977</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0003295464007724441</v>
+        <v>0.0003295464007724416</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003147001056241605</v>
+        <v>0.000314700105624165</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004114717750221144</v>
+        <v>0.0004114717750221192</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0004823379435787246</v>
+        <v>0.0004823379435787267</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008117121095843964</v>
+        <v>0.0008117121095843966</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0006197256657696944</v>
+        <v>0.0006197256657696913</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001321453498017408</v>
+        <v>0.001321453498017407</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0005973718738569029</v>
+        <v>0.0005973718738569014</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0002580555367952114</v>
+        <v>0.0002580555367952116</v>
       </c>
       <c r="P6" t="n">
-        <v>0.000431621399727645</v>
+        <v>0.000431621399727644</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0003533991312812102</v>
+        <v>0.0003533991312812106</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0002940249576294753</v>
+        <v>0.0002940249576294752</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003769506942739168</v>
+        <v>0.0003769506942739172</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0003161743628192333</v>
+        <v>0.0003161743628192326</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001041983556838968</v>
+        <v>0.001041983556838967</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002122617287534364</v>
+        <v>0.0002122617287534361</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0007944000153916383</v>
+        <v>0.0007944000153916359</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0007394361456651</v>
+        <v>0.0007394361456651004</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0004446356779984348</v>
+        <v>0.0004446356779984359</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0003749111847616589</v>
+        <v>0.0003749111847616562</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0007042323762528966</v>
+        <v>0.0007042323762528942</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003700503189370485</v>
+        <v>0.003700503189370481</v>
       </c>
     </row>
     <row r="7">
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001619122114732471</v>
+        <v>0.0001619122114732514</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002147805106378305</v>
+        <v>0.0002147805106378302</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002117515624308803</v>
+        <v>0.0002117515624308787</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001797991678020733</v>
+        <v>0.0001797991678020725</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000165998434565918</v>
+        <v>0.0001659984345659178</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002123363718699097</v>
+        <v>0.0002123363718699136</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002117515624308803</v>
+        <v>0.0002117515624308787</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002117515624308803</v>
+        <v>0.0002117515624308787</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002001166596800944</v>
+        <v>0.0002001166596800934</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002117515624308803</v>
+        <v>0.0002117515624308787</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002117515624308803</v>
+        <v>0.0002117515624308787</v>
       </c>
       <c r="M7" t="n">
         <v>0.0002157665193990486</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001731177274968963</v>
+        <v>0.0001731177274968944</v>
       </c>
       <c r="O7" t="n">
-        <v>0.000173984936133556</v>
+        <v>0.0001739849361335595</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001713824741451289</v>
+        <v>0.0001713824741451302</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001521176414824454</v>
+        <v>0.0001521176414824468</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0002117515624308803</v>
+        <v>0.0002117515624308787</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002117515624308803</v>
+        <v>0.0002117515624308787</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0002117515624308803</v>
+        <v>0.0002117515624308787</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001776506218088543</v>
+        <v>0.0001776506218088528</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001825152118957454</v>
+        <v>0.0001825152118957443</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0002020116526361359</v>
+        <v>0.0002020116526361348</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0001469358123747729</v>
+        <v>0.0001469358123747692</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0002612623898457976</v>
+        <v>0.0002612623898458013</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001609864199416582</v>
+        <v>0.0001609864199416611</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0002117515624308803</v>
+        <v>0.0002117515624308787</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.000292674748866122</v>
+        <v>0.0002926747488661225</v>
       </c>
     </row>
   </sheetData>
@@ -4690,85 +4690,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0003029983278083177</v>
+        <v>0.0003029983278083035</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003683890935055564</v>
+        <v>0.000368389093505557</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0005680580421949376</v>
+        <v>0.0005680580421949246</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004742511041836827</v>
+        <v>0.0004742511041836818</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0004582891821024478</v>
+        <v>0.0004582891821024476</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0004301247501575435</v>
+        <v>0.0004301247501575147</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0004822282243613589</v>
+        <v>0.000482228224361345</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0004882717161347156</v>
+        <v>0.0004882717161347045</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0005441522038627912</v>
+        <v>0.0005441522038627806</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004448863019930292</v>
+        <v>0.000444886301993016</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005007723591706497</v>
+        <v>0.0005007723591706349</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003475644273738492</v>
+        <v>0.0003475644273738485</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0004976562632256648</v>
+        <v>0.0004976562632256533</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0005265448165305068</v>
+        <v>0.000526544816530493</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0004927175251187089</v>
+        <v>0.0004927175251186953</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002887784369804022</v>
+        <v>0.0002887784369803913</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007070071935852731</v>
+        <v>0.0007070071935852575</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0005483876504401095</v>
+        <v>0.0005483876504400955</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0003091339122301885</v>
+        <v>0.0003091339122301902</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0003251475945737696</v>
+        <v>0.0003251475945737547</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0005063211834491893</v>
+        <v>0.0005063211834491717</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0008776418232248731</v>
+        <v>0.0008776418232248592</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0036459121854826</v>
+        <v>0.003645912185482587</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.002468554409909282</v>
+        <v>0.002468554409909267</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0006165169972216462</v>
+        <v>0.0006165169972216312</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.000923771936989385</v>
+        <v>0.0009237719369893712</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0001993564849459592</v>
+        <v>0.0001993564849459584</v>
       </c>
     </row>
     <row r="3">
@@ -4778,85 +4778,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000275105326443412</v>
+        <v>0.00027510532644341</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004116827620716168</v>
+        <v>0.000411682762071609</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004070818019185422</v>
+        <v>0.0004070818019185167</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003324472717806645</v>
+        <v>0.0003324472717806626</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000293455816066926</v>
+        <v>0.0002934558160669247</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000434447983855259</v>
+        <v>0.000434447983855258</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0004070818019185422</v>
+        <v>0.0004070818019185167</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004070818019185422</v>
+        <v>0.0004070818019185167</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004050013639852129</v>
+        <v>0.0004050013639851994</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004070818019185422</v>
+        <v>0.0004070818019185167</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004070818019185422</v>
+        <v>0.0004070818019185167</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000403740803381749</v>
+        <v>0.0004037408033817472</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0003047779542427092</v>
+        <v>0.0003047779542427056</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000332891939875205</v>
+        <v>0.0003328919398751857</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003260005226673427</v>
+        <v>0.0003260005226673376</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002491689367957603</v>
+        <v>0.0002491689367957633</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0004070818019185422</v>
+        <v>0.0004070818019185167</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004070818019185422</v>
+        <v>0.0004070818019185167</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0004070818019185422</v>
+        <v>0.0004070818019185167</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0003426000449210914</v>
+        <v>0.0003426000449210876</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0003660826718490546</v>
+        <v>0.0003660826718490395</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0004071077390806171</v>
+        <v>0.0004071077390805977</v>
       </c>
       <c r="X3" t="n">
-        <v>0.000261264843016189</v>
+        <v>0.0002612648430161753</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0005381904414980324</v>
+        <v>0.0005381904414980169</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0002726537956543942</v>
+        <v>0.0002726537956543883</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0004070818019185422</v>
+        <v>0.0004070818019185167</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0005410647451157537</v>
+        <v>0.0005410647451157508</v>
       </c>
     </row>
     <row r="4">
@@ -4866,85 +4866,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002758266908890314</v>
+        <v>0.002758266908890299</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002785025039334303</v>
+        <v>0.002785025039334292</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002854878062295929</v>
+        <v>0.002854878062295917</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002817915099987764</v>
+        <v>0.002817915099987763</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002813464182574819</v>
+        <v>0.002813464182574817</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00280460299704278</v>
+        <v>0.002804602997042768</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002823594101560192</v>
+        <v>0.002823594101560177</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002825796883345319</v>
+        <v>0.002825796883345305</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002728206529311896</v>
+        <v>0.002728206529311897</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002809983409347926</v>
+        <v>0.002809983409347914</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002830353220941953</v>
+        <v>0.002830353220941939</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002772387485058278</v>
+        <v>0.002772387485058276</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002829217440561057</v>
+        <v>0.002829217440561042</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002839746979014147</v>
+        <v>0.002839746979014134</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002827417328514656</v>
+        <v>0.002827417328514646</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002753083925661926</v>
+        <v>0.002753083925661935</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00290552339635439</v>
+        <v>0.002905523396354375</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002847708435482693</v>
+        <v>0.002847708435482681</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002760503257364415</v>
+        <v>0.00276050325736441</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002766340056536498</v>
+        <v>0.002766340056536481</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002051124457007452</v>
+        <v>0.002051124457007438</v>
       </c>
       <c r="W4" t="n">
-        <v>0.00296771771516504</v>
+        <v>0.002967717715165026</v>
       </c>
       <c r="X4" t="n">
-        <v>0.003976719755536196</v>
+        <v>0.003976719755536183</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00354758667157273</v>
+        <v>0.003547586671572719</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002872540782369383</v>
+        <v>0.00287254078236937</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002984531599945061</v>
+        <v>0.00298453159994505</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002718026463978917</v>
+        <v>0.002718026463978916</v>
       </c>
     </row>
     <row r="5">
@@ -4954,85 +4954,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002748100237428963</v>
+        <v>0.002748100237428921</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002800805073146707</v>
+        <v>0.002800805073146692</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002796204112993627</v>
+        <v>0.002796204112993607</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002766229268221532</v>
+        <v>0.002766229268221533</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002753384356225974</v>
+        <v>0.002753384356225973</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002806178764959627</v>
+        <v>0.002806178764959616</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002796204112993627</v>
+        <v>0.002796204112993607</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002796204112993627</v>
+        <v>0.002796204112993607</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002677487682168178</v>
+        <v>0.002677487682168174</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002796204112993627</v>
+        <v>0.002796204112993607</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002796204112993627</v>
+        <v>0.002796204112993607</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002792863114456844</v>
+        <v>0.002792863114456845</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002758915561828214</v>
+        <v>0.002758915561828209</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002769162779460173</v>
+        <v>0.002769162779460177</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002766650938811012</v>
+        <v>0.002766650938811013</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002738646727962857</v>
+        <v>0.002738646727962845</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002796204112993627</v>
+        <v>0.002796204112993607</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002796204112993627</v>
+        <v>0.002796204112993607</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002796204112993627</v>
+        <v>0.002796204112993607</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002772701269751072</v>
+        <v>0.002772701269751068</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00200000916629294</v>
+        <v>0.002000009166292933</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002796213566784635</v>
+        <v>0.002796213566784624</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002743055543742904</v>
+        <v>0.002743055543742883</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002843991672564975</v>
+        <v>0.002843991672564961</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002747206683243691</v>
+        <v>0.002747206683243687</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002796204112993627</v>
+        <v>0.002796204112993607</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.002842575112269826</v>
+        <v>0.002842575112269824</v>
       </c>
     </row>
     <row r="6">
@@ -5042,85 +5042,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001628514423356959</v>
+        <v>0.0001628514423356863</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001896095727796864</v>
+        <v>0.0001896095727796819</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0002594625957413101</v>
+        <v>0.0002594625957412993</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0002224996334331506</v>
+        <v>0.00022249963343315</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002180487160202033</v>
+        <v>0.0002180487160202032</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001996059984370664</v>
+        <v>0.0001996059984370485</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0002281786350055762</v>
+        <v>0.0002281786350055648</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0002303814167907027</v>
+        <v>0.0002303814167906922</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002402256378861086</v>
+        <v>0.0002402256378860966</v>
       </c>
       <c r="K6" t="n">
-        <v>0.000214567942793311</v>
+        <v>0.0002145679427933004</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002349377543873374</v>
+        <v>0.0002349377543873282</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0001769720185036654</v>
+        <v>0.0001769720185036647</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0002338019740064348</v>
+        <v>0.0002338019740064276</v>
       </c>
       <c r="O6" t="n">
-        <v>0.000234749980408427</v>
+        <v>0.0002347499804084166</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0002224203299089373</v>
+        <v>0.0002224203299089254</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001576684591073091</v>
+        <v>0.0001576684591073207</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003101079297997737</v>
+        <v>0.0003101079297997639</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0002522929689280764</v>
+        <v>0.0002522929689280655</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001650877908097981</v>
+        <v>0.0001650877908097959</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0001613430579307768</v>
+        <v>0.0001613430579307667</v>
       </c>
       <c r="V6" t="n">
-        <v>0.000224875252017545</v>
+        <v>0.000224875252017546</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0003627207165593205</v>
+        <v>0.000362720716559309</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001371722756930478</v>
+        <v>0.001371722756930467</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0009521712050181146</v>
+        <v>0.0009521712050181042</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0002771253158147658</v>
+        <v>0.0002771253158147546</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0003891161333904457</v>
+        <v>0.0003891161333904357</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0001226109974242984</v>
+        <v>0.0001226109974242978</v>
       </c>
     </row>
     <row r="7">
@@ -5130,85 +5130,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001526847708743471</v>
+        <v>0.0001526847708743099</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002053896065920923</v>
+        <v>0.000205389606592082</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002007886464390098</v>
+        <v>0.0002007886464389963</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001708138016669202</v>
+        <v>0.0001708138016669192</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001579688896713626</v>
+        <v>0.0001579688896713618</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002011817663539103</v>
+        <v>0.0002011817663538956</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002007886464390098</v>
+        <v>0.0002007886464389963</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002007886464390098</v>
+        <v>0.0002007886464389963</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001895067907423891</v>
+        <v>0.0001895067907423747</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002007886464390098</v>
+        <v>0.0002007886464389963</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002007886464390098</v>
+        <v>0.0002007886464389963</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0001974476479022332</v>
+        <v>0.0001974476479022322</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001635000952736055</v>
+        <v>0.0001635000952735994</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001641657808544565</v>
+        <v>0.0001641657808544563</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001616539402052972</v>
+        <v>0.0001616539402052949</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001432312614082369</v>
+        <v>0.0001432312614082337</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0002007886464390098</v>
+        <v>0.0002007886464389963</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002007886464390098</v>
+        <v>0.0002007886464389963</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0002007886464390098</v>
+        <v>0.0002007886464389963</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001677042711453558</v>
+        <v>0.0001677042711453511</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001737599613030443</v>
+        <v>0.0001737599613030361</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001912165681789168</v>
+        <v>0.0001912165681789061</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0001380585451371777</v>
+        <v>0.0001380585451371631</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0002485762060103617</v>
+        <v>0.0002485762060103479</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001517912166890832</v>
+        <v>0.0001517912166890731</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0002007886464390098</v>
+        <v>0.0002007886464389963</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0002471596457152129</v>
+        <v>0.0002471596457152117</v>
       </c>
     </row>
   </sheetData>
@@ -5374,85 +5374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.000407424949220191</v>
+        <v>0.0004074249492201876</v>
       </c>
       <c r="C2" t="n">
         <v>0.0003632182547899473</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0005075977266608593</v>
+        <v>0.0005075977266608525</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0005957409389021526</v>
+        <v>0.0005957409389021528</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0004311097613842259</v>
+        <v>0.000431109761384226</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003663910579347732</v>
+        <v>0.0003663910579347691</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003979378330655497</v>
+        <v>0.0003979378330655606</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003944816663404902</v>
+        <v>0.0003944816663404868</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0005172497046045853</v>
+        <v>0.0005172497046045949</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000379297623022676</v>
+        <v>0.0003792976230226725</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005215433143646698</v>
+        <v>0.0005215433143646671</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003415516381815224</v>
+        <v>0.0003415516381815263</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0003915628905219076</v>
+        <v>0.0003915628905219041</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0006815646413093382</v>
+        <v>0.0006815646413093336</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0005502385696323783</v>
+        <v>0.0005502385696323832</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002938227362712588</v>
+        <v>0.0002938227362712545</v>
       </c>
       <c r="R2" t="n">
-        <v>0.000712382227204173</v>
+        <v>0.00071238222720417</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0005020325740555833</v>
+        <v>0.0005020325740555708</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0002964672584604721</v>
+        <v>0.0002964672584604676</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0003535693781088349</v>
+        <v>0.0003535693781088296</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0005938360464344646</v>
+        <v>0.000593836046434465</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0006988448270942203</v>
+        <v>0.0006988448270942165</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004690757947095546</v>
+        <v>0.00469075794709554</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.002218707642877764</v>
+        <v>0.002218707642877763</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0005153194622447465</v>
+        <v>0.0005153194622447383</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0009506925016297383</v>
+        <v>0.000950692501629739</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0002947765346043609</v>
+        <v>0.0002947765346043071</v>
       </c>
     </row>
     <row r="3">
@@ -5462,85 +5462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0002734750417005218</v>
+        <v>0.0002734750417005244</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004098540065499882</v>
+        <v>0.000409854006549988</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004050246339379652</v>
+        <v>0.0004050246339379598</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003311533204278639</v>
+        <v>0.0003311533204278635</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0002919365844063105</v>
+        <v>0.0002919365844063106</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004323022988545772</v>
+        <v>0.0004323022988545759</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0004050246339379652</v>
+        <v>0.0004050246339379598</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004050246339379652</v>
+        <v>0.0004050246339379598</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004031523746964354</v>
+        <v>0.0004031523746964416</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004050246339379652</v>
+        <v>0.0004050246339379598</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004050246339379652</v>
+        <v>0.0004050246339379598</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004019379720327606</v>
+        <v>0.0004019379720327627</v>
       </c>
       <c r="N3" t="n">
-        <v>0.000303051692187721</v>
+        <v>0.0003030516921877127</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0003310747419994145</v>
+        <v>0.000331074741999392</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003242056153584529</v>
+        <v>0.0003242056153584512</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002476225443518164</v>
+        <v>0.0002476225443518072</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0004050246339379652</v>
+        <v>0.0004050246339379598</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004050246339379652</v>
+        <v>0.0004050246339379598</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0004050246339379652</v>
+        <v>0.0004050246339379598</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0003407543385125702</v>
+        <v>0.0003407543385125744</v>
       </c>
       <c r="V3" t="n">
-        <v>0.000364625282544908</v>
+        <v>0.0003646252825449076</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0004050504872067135</v>
+        <v>0.0004050504872066887</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0002596793258761656</v>
+        <v>0.0002596793258761672</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0005357141459415204</v>
+        <v>0.0005357141459415085</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.000271031440486671</v>
+        <v>0.0002710314404866726</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0004050246339379652</v>
+        <v>0.0004050246339379598</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0005391696821942058</v>
+        <v>0.0005391696821942374</v>
       </c>
     </row>
     <row r="4">
@@ -5550,85 +5550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002790855713114598</v>
+        <v>0.002790855713114593</v>
       </c>
       <c r="C4" t="n">
         <v>0.002777812015100288</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00282736751420358</v>
+        <v>0.002827367514203571</v>
       </c>
       <c r="E4" t="n">
         <v>0.00285706382467003</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002798196969080505</v>
+        <v>0.002798196969080504</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002775899341585346</v>
+        <v>0.002775899341585339</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002787397770679579</v>
+        <v>0.002787397770679575</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002786138038492647</v>
+        <v>0.002786138038492641</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002720672221552168</v>
+        <v>0.002720672221552164</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002780603633003347</v>
+        <v>0.002780603633003332</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002832450517164261</v>
+        <v>0.002832450517164256</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002764884054878317</v>
+        <v>0.002764884054878321</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002785074178980774</v>
+        <v>0.002785074178980767</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002890776411770303</v>
+        <v>0.002890776411770299</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002842909600752654</v>
+        <v>0.00284290960075264</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002749449040479248</v>
+        <v>0.00274944904047924</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002902009059950607</v>
+        <v>0.002902009059950599</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002825339081428277</v>
+        <v>0.002825339081428267</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002750412937763669</v>
+        <v>0.002750412937763662</v>
       </c>
       <c r="U4" t="n">
-        <v>0.002771225989848555</v>
+        <v>0.002771225989848543</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002128642713685644</v>
+        <v>0.002128642713685649</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002897074836574705</v>
+        <v>0.0028970748365747</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004352080293404707</v>
+        <v>0.004352080293404688</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003451046985797564</v>
+        <v>0.003451046985797557</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002830181996150712</v>
+        <v>0.002830181996150707</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002988870356598199</v>
+        <v>0.00298887035659819</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002747718882596662</v>
+        <v>0.002747718882596563</v>
       </c>
     </row>
     <row r="5">
@@ -5638,85 +5638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002742032544742912</v>
+        <v>0.002742032544742907</v>
       </c>
       <c r="C5" t="n">
         <v>0.002794810198992176</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00278998082638015</v>
+        <v>0.002789980826380151</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002760624744680833</v>
+        <v>0.002760624744680831</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002747469980326008</v>
+        <v>0.002747469980326006</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002799923214931739</v>
+        <v>0.002799923214931748</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00278998082638015</v>
+        <v>0.002789980826380151</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00278998082638015</v>
+        <v>0.002789980826380151</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002679085084599144</v>
+        <v>0.002679085084599135</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00278998082638015</v>
+        <v>0.002789980826380151</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00278998082638015</v>
+        <v>0.002789980826380151</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002786894164474962</v>
+        <v>0.002786894164474965</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002752812886538915</v>
+        <v>0.002752812886538912</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002763026959132006</v>
+        <v>0.002763026959132012</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002760523243132768</v>
+        <v>0.002760523243132749</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002732609613034652</v>
+        <v>0.002732609613034646</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00278998082638015</v>
+        <v>0.002789980826380151</v>
       </c>
       <c r="S5" t="n">
-        <v>0.00278998082638015</v>
+        <v>0.002789980826380151</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00278998082638015</v>
+        <v>0.002789980826380151</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002766555058397504</v>
+        <v>0.0027665550583975</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002045098081776572</v>
+        <v>0.002045098081776581</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002789990249593015</v>
+        <v>0.002789990249593016</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002737004168322409</v>
+        <v>0.002737004168322393</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002837615618871718</v>
+        <v>0.00283761561887171</v>
       </c>
       <c r="Z5" t="n">
         <v>0.00274114188079467</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00278998082638015</v>
+        <v>0.002789980826380151</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00283679731508393</v>
+        <v>0.002836797315083868</v>
       </c>
     </row>
     <row r="6">
@@ -5726,85 +5726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00020026623440279</v>
+        <v>0.0002002662344027697</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001872225363884635</v>
+        <v>0.0001872225363884634</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0002367780354917717</v>
+        <v>0.0002367780354917523</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0002664743459582079</v>
+        <v>0.0002664743459582078</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0002076074903686803</v>
+        <v>0.0002076074903686805</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001757667170036554</v>
+        <v>0.0001757667170036531</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000196808291967769</v>
+        <v>0.0001968082919677509</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001955485597808406</v>
+        <v>0.00019554855978082</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002299395559791995</v>
+        <v>0.0002299395559791924</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0001900141542915354</v>
+        <v>0.000190014154291509</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002418610384524537</v>
+        <v>0.0002418610384524333</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0001742945761664953</v>
+        <v>0.0001742945761664981</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0001944847002689628</v>
+        <v>0.0001944847002689427</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0002906437871886169</v>
+        <v>0.0002906437871886124</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0002427769761709687</v>
+        <v>0.000242776976170953</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001588595617674375</v>
+        <v>0.0001588595617674183</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003114195812387965</v>
+        <v>0.0003114195812387767</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0002347496027164693</v>
+        <v>0.0002347496027164436</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001598234590518581</v>
+        <v>0.000159823459051839</v>
       </c>
       <c r="U6" t="n">
-        <v>0.000171093365266868</v>
+        <v>0.0001710933652668582</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002564615002413825</v>
+        <v>0.0002564615002413826</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0002969422119930207</v>
+        <v>0.0002969422119930153</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001751947668823021</v>
+        <v>0.001751947668823003</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0008604575070857535</v>
+        <v>0.0008604575070857316</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0002395925174388944</v>
+        <v>0.0002395925174388806</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0003982808778863884</v>
+        <v>0.0003982808778863657</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0001571294038848386</v>
+        <v>0.0001571294038847812</v>
       </c>
     </row>
     <row r="7">
@@ -5814,85 +5814,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001514430660310871</v>
+        <v>0.0001514430660310852</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002042207202803529</v>
+        <v>0.0002042207202803527</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001993913476683281</v>
+        <v>0.0001993913476683249</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001700352659690088</v>
+        <v>0.0001700352659690085</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001568805016141842</v>
+        <v>0.0001568805016141843</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001997905903500531</v>
+        <v>0.000199790590350062</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001993913476683281</v>
+        <v>0.0001993913476683249</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001993913476683281</v>
+        <v>0.0001993913476683249</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001883524190261671</v>
+        <v>0.0001883524190261634</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001993913476683281</v>
+        <v>0.0001993913476683249</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001993913476683281</v>
+        <v>0.0001993913476683249</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0001963046857631365</v>
+        <v>0.0001963046857631411</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001622234078271092</v>
+        <v>0.0001622234078270893</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001628943345503247</v>
+        <v>0.0001628943345503297</v>
       </c>
       <c r="P7" t="n">
-        <v>0.000160390618551081</v>
+        <v>0.0001603906185510641</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.000142020134322831</v>
+        <v>0.0001420201343228236</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001993913476683281</v>
+        <v>0.0001993913476683249</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001993913476683281</v>
+        <v>0.0001993913476683249</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0001993913476683281</v>
+        <v>0.0001993913476683249</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001664224338158212</v>
+        <v>0.0001664224338158165</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001729168683323181</v>
+        <v>0.000172916868332318</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001898576250113288</v>
+        <v>0.0001898576250113306</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0001368715437407247</v>
+        <v>0.0001368715437407092</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0002470261401599066</v>
+        <v>0.0002470261401598875</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001505524020828373</v>
+        <v>0.0001505524020828469</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0001993913476683281</v>
+        <v>0.0001993913476683249</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.000246207836372107</v>
+        <v>0.000246207836372044</v>
       </c>
     </row>
   </sheetData>
@@ -6058,85 +6058,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001694189456900048</v>
+        <v>0.001694189456900098</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000428395032895667</v>
+        <v>0.0004283950328957374</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002549716676958941</v>
+        <v>0.002549716676958988</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000961489215983249</v>
+        <v>0.0009614892159832809</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0009208617583746126</v>
+        <v>0.0009208617583746125</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002025316697799698</v>
+        <v>0.002025316697799751</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000826187587363759</v>
+        <v>0.0008261875873638055</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002002505994372394</v>
+        <v>0.002002505994372437</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002659049260655588</v>
+        <v>0.002659049260655601</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003117551278376535</v>
+        <v>0.003117551278376575</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003692030060592995</v>
+        <v>0.003692030060593042</v>
       </c>
       <c r="M2" t="n">
         <v>0.01018277994725973</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002679072991845662</v>
+        <v>0.002679072991845704</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001327032653120519</v>
+        <v>0.001327032653120557</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001752933644336314</v>
+        <v>0.001752933644336335</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001018461399395819</v>
+        <v>0.001018461399395863</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001051950771485761</v>
+        <v>0.001051950771485725</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001892807283284768</v>
+        <v>0.001892807283284813</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001824923715038655</v>
+        <v>0.001824923715038702</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00565400221613167</v>
+        <v>0.005654002216131733</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008011816543951666</v>
+        <v>0.000801181654395168</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002830260264435047</v>
+        <v>0.002830260264435108</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007428728771744675</v>
+        <v>0.00742872877174474</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.005541705227376776</v>
+        <v>0.005541705227376821</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001324550471410103</v>
+        <v>0.001324550471410142</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.003004850265541887</v>
+        <v>0.003004850265541933</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.008655036368346568</v>
+        <v>0.008655036368346566</v>
       </c>
     </row>
     <row r="3">
@@ -6146,85 +6146,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0003163907489050595</v>
+        <v>0.0003163907489051337</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004620580593734269</v>
+        <v>0.0004620580593734414</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004608289090092504</v>
+        <v>0.0004608289090092956</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003760622474003943</v>
+        <v>0.0003760622474004237</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0003340311291992598</v>
+        <v>0.0003340311291992595</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004907791024336611</v>
+        <v>0.0004907791024336629</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0004608289090092504</v>
+        <v>0.0004608289090092956</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004608289090092504</v>
+        <v>0.0004608289090092956</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004582407601521239</v>
+        <v>0.0004582407601521286</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004608289090092504</v>
+        <v>0.0004608289090092956</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004608289090092504</v>
+        <v>0.0004608289090092956</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004808278280092084</v>
+        <v>0.0004808278280092082</v>
       </c>
       <c r="N3" t="n">
-        <v>0.000348865170949869</v>
+        <v>0.0003488651709499124</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0003796337783318841</v>
+        <v>0.0003796337783319081</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003720916491889083</v>
+        <v>0.0003720916491889667</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002880053538055037</v>
+        <v>0.0002880053538055033</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0004608289090092504</v>
+        <v>0.0004608289090092956</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004608289090092504</v>
+        <v>0.0004608289090092956</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0004608289090092504</v>
+        <v>0.0004608289090092956</v>
       </c>
       <c r="U3" t="n">
-        <v>0.000390281723887787</v>
+        <v>0.000390281723887774</v>
       </c>
       <c r="V3" t="n">
-        <v>0.000412335769362354</v>
+        <v>0.0004123357693623679</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0004608572952430414</v>
+        <v>0.0004608572952431206</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0003012433981800172</v>
+        <v>0.0003012433981800652</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0006043569210257125</v>
+        <v>0.0006043569210257279</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0003137077359268103</v>
+        <v>0.0003137077359268047</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0004608289090092504</v>
+        <v>0.0004608289090092956</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.00063308460465835</v>
+        <v>0.0006330846046583506</v>
       </c>
     </row>
     <row r="4">
@@ -6234,85 +6234,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003394175210959089</v>
+        <v>0.003394175210959184</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002933589146607912</v>
+        <v>0.002933589146607993</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003706004836562726</v>
+        <v>0.003706004836562835</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003122120978597505</v>
+        <v>0.003122120978597558</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003109216870862079</v>
+        <v>0.003109216870862101</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003514867201974646</v>
+        <v>0.00351486720197472</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003077798722105669</v>
+        <v>0.003077798722105756</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003506552968432194</v>
+        <v>0.003506552968432307</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003611165214438532</v>
+        <v>0.003611165214438538</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003912973880928915</v>
+        <v>0.003912973880928996</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004122364651176361</v>
+        <v>0.004122364651176445</v>
       </c>
       <c r="M4" t="n">
-        <v>0.006500876314496743</v>
+        <v>0.006500876314496801</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003753153694360411</v>
+        <v>0.003753153694360487</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003260350867354317</v>
+        <v>0.003260350867354398</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003415586777470546</v>
+        <v>0.003415586777470626</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.003147880268798276</v>
+        <v>0.003147880268798357</v>
       </c>
       <c r="R4" t="n">
-        <v>0.003160086751672991</v>
+        <v>0.003160086751673074</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003466569076388058</v>
+        <v>0.003466569076388134</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00344182631289145</v>
+        <v>0.003441826312891544</v>
       </c>
       <c r="U4" t="n">
-        <v>0.004837480463229988</v>
+        <v>0.004837480463230079</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002175344709021955</v>
+        <v>0.002175344709021948</v>
       </c>
       <c r="W4" t="n">
-        <v>0.003808259679888648</v>
+        <v>0.003808259679888764</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005484347452859562</v>
+        <v>0.005484347452859657</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.004796549529486658</v>
+        <v>0.004796549529486763</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.003259446141268116</v>
+        <v>0.003259446141268218</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003871895685152793</v>
+        <v>0.003871895685152891</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.005944908116212739</v>
+        <v>0.00594490811621277</v>
       </c>
     </row>
     <row r="5">
@@ -6322,85 +6322,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002891983760824183</v>
+        <v>0.002891983760824316</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002945858924467846</v>
+        <v>0.0029458589244679</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00294462977410367</v>
+        <v>0.002944629774103736</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002908739722979593</v>
+        <v>0.00290873972297968</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002895323997440808</v>
+        <v>0.00289532399744083</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002955546267913935</v>
+        <v>0.002955546267914006</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00294462977410367</v>
+        <v>0.002944629774103736</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00294462977410367</v>
+        <v>0.002944629774103736</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002808996359203197</v>
+        <v>0.002808996359203288</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00294462977410367</v>
+        <v>0.002944629774103736</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00294462977410367</v>
+        <v>0.002944629774103736</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002964628693103605</v>
+        <v>0.002964628693103634</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002903820306325613</v>
+        <v>0.002903820306325677</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00291503510241313</v>
+        <v>0.002915035102413152</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002912286084904664</v>
+        <v>0.002912286084904707</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002881637617628544</v>
+        <v>0.002881637617628619</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00294462977410367</v>
+        <v>0.002944629774103736</v>
       </c>
       <c r="S5" t="n">
-        <v>0.00294462977410367</v>
+        <v>0.002944629774103736</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00294462977410367</v>
+        <v>0.002944629774103736</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002918916153533773</v>
+        <v>0.002918916153533856</v>
       </c>
       <c r="V5" t="n">
-        <v>0.00203361494998641</v>
+        <v>0.002033614949986423</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002944640120552553</v>
+        <v>0.002944640120552617</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002886462729354103</v>
+        <v>0.002886462729354205</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.002996944049092658</v>
+        <v>0.002996944049092679</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00289100583409916</v>
+        <v>0.002891005834099263</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00294462977410367</v>
+        <v>0.002944629774103736</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003021000896861853</v>
+        <v>0.003021000896861902</v>
       </c>
     </row>
     <row r="6">
@@ -6410,85 +6410,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0006840614874163588</v>
+        <v>0.0006840614874164178</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0002234754230651984</v>
+        <v>0.0002234754230652113</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0009958911130200023</v>
+        <v>0.0009958911130200606</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0004120072550547705</v>
+        <v>0.0004120072550547972</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0003991031473193381</v>
+        <v>0.0003991031473193374</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0007948079994187023</v>
+        <v>0.0007948079994187514</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003676849985629386</v>
+        <v>0.0003676849985629915</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0007964392448894648</v>
+        <v>0.0007964392448895149</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001024548141313101</v>
+        <v>0.001024548141313132</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001202860157386184</v>
+        <v>0.00120286015738623</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00141225092763364</v>
+        <v>0.001412250927633684</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003790762590954016</v>
+        <v>0.003790762590954017</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001043039970817675</v>
+        <v>0.001043039970817728</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0005402916647983752</v>
+        <v>0.0005402916647984261</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0006955275749145906</v>
+        <v>0.000695527574914627</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0004377665452555336</v>
+        <v>0.0004377665452555864</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0004499730281302546</v>
+        <v>0.0004499730281303215</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0007564553528453251</v>
+        <v>0.0007564553528453743</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0007317125893487213</v>
+        <v>0.0007317125893487717</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002117421260674043</v>
+        <v>0.002117421260674087</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0003435397235015632</v>
+        <v>0.0003435397235015545</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001088200477332708</v>
+        <v>0.001088200477332786</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002764288250303618</v>
+        <v>0.002764288250303677</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002086435805943926</v>
+        <v>0.002086435805943978</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0005493324177253856</v>
+        <v>0.0005493324177254388</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001161781961610066</v>
+        <v>0.001161781961610117</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003234794392669993</v>
+        <v>0.003234794392669996</v>
       </c>
     </row>
     <row r="7">
@@ -6498,85 +6498,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001818700372814545</v>
+        <v>0.0001818700372815293</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002357452009251023</v>
+        <v>0.0002357452009251201</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002345160505609338</v>
+        <v>0.0002345160505609792</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001986259994368602</v>
+        <v>0.0001986259994368862</v>
       </c>
       <c r="F7" t="n">
         <v>0.0001852102738980773</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002354870653579857</v>
+        <v>0.0002354870653580267</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002345160505609338</v>
+        <v>0.0002345160505609792</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002345160505609338</v>
+        <v>0.0002345160505609792</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002223792860777674</v>
+        <v>0.0002223792860777912</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002345160505609338</v>
+        <v>0.0002345160505609792</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002345160505609338</v>
+        <v>0.0002345160505609792</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002545149695608686</v>
+        <v>0.0002545149695608685</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001937065827828821</v>
+        <v>0.0001937065827829077</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001949758998571783</v>
+        <v>0.0001949758998571798</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001922268823487099</v>
+        <v>0.0001922268823487205</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001715238940858122</v>
+        <v>0.0001715238940858476</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0002345160505609338</v>
+        <v>0.0002345160505609792</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002345160505609338</v>
+        <v>0.0002345160505609792</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0002345160505609338</v>
+        <v>0.0002345160505609792</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001988569509778191</v>
+        <v>0.0001988569509778607</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0002018099644660211</v>
+        <v>0.0002018099644660122</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0002245809179966129</v>
+        <v>0.0002245809179966567</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0001664035267981461</v>
+        <v>0.0001664035267982088</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0002868303255499173</v>
+        <v>0.0002868303255499149</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001808921105564177</v>
+        <v>0.0001808921105564757</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0002345160505609338</v>
+        <v>0.0002345160505609792</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0003108871733191217</v>
+        <v>0.000310887173319122</v>
       </c>
     </row>
   </sheetData>
@@ -6742,79 +6742,79 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0002463774699449773</v>
+        <v>0.000246377469944979</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003155078123640656</v>
+        <v>0.0003155078123640657</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0006508753657608889</v>
+        <v>0.0006508753657608908</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000496566949297544</v>
+        <v>0.0004965669492975447</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0003817414940407327</v>
+        <v>0.0003817414940407324</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001712917659738652</v>
+        <v>0.001712917659738653</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003894667080254896</v>
+        <v>0.0003894667080254907</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000506675430021248</v>
+        <v>0.0005066754300212501</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001565212554642987</v>
+        <v>0.00156521255464298</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000775275325978205</v>
+        <v>0.0007752753259782067</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001628881733501483</v>
+        <v>0.001628881733501484</v>
       </c>
       <c r="M2" t="n">
         <v>0.001118210319377129</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0005915866237027638</v>
+        <v>0.0005915866237027654</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0004755854092715784</v>
+        <v>0.0004755854092715802</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001290437905172075</v>
+        <v>0.001290437905172076</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0005389898521151995</v>
+        <v>0.0005389898521152016</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007391102540097484</v>
+        <v>0.00073911025400975</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007267381049329793</v>
+        <v>0.0007267381049329815</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0004144698003778018</v>
+        <v>0.0004144698003778023</v>
       </c>
       <c r="U2" t="n">
-        <v>0.00109681574506829</v>
+        <v>0.001096815745068291</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0004353263237762322</v>
+        <v>0.0004353263237762318</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001235834455452901</v>
+        <v>0.001235834455452902</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007882808038683861</v>
+        <v>0.007882808038683865</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.009895733695162204</v>
+        <v>0.009895733695162208</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0005526285466561076</v>
+        <v>0.0005526285466561092</v>
       </c>
       <c r="AA2" t="n">
         <v>0.0009779876917829489</v>
@@ -6830,85 +6830,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0002962845696327152</v>
+        <v>0.0002962845696327172</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000438924283318403</v>
+        <v>0.0004389242833184032</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004350069504416118</v>
+        <v>0.0004350069504416139</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003557669635013487</v>
+        <v>0.0003557669635013488</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0003144370138501404</v>
+        <v>0.0003144370138501406</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004637719397945478</v>
+        <v>0.0004637719397945502</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0004350069504416118</v>
+        <v>0.0004350069504416139</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004350069504416118</v>
+        <v>0.0004350069504416139</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004330961887744757</v>
+        <v>0.0004330961887744771</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004350069504416118</v>
+        <v>0.0004350069504416139</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004350069504416118</v>
+        <v>0.0004350069504416139</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004329774038694067</v>
+        <v>0.0004329774038694071</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0003274738975658682</v>
+        <v>0.0003274738975658698</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0003570249141899364</v>
+        <v>0.0003570249141899376</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003497812459626917</v>
+        <v>0.0003497812459626947</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002690224556201669</v>
+        <v>0.0002690224556201692</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0004350069504416118</v>
+        <v>0.0004350069504416139</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004350069504416118</v>
+        <v>0.0004350069504416139</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0004350069504416118</v>
+        <v>0.0004350069504416139</v>
       </c>
       <c r="U3" t="n">
-        <v>0.000367219930595133</v>
+        <v>0.0003672199305951344</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0003908388973073704</v>
+        <v>0.0003908388973073706</v>
       </c>
       <c r="W3" t="n">
-        <v>0.000435034213363931</v>
+        <v>0.0004350342133639335</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0002817366374666645</v>
+        <v>0.000281736637466666</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0005728012043603526</v>
+        <v>0.0005728012043603545</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0002937077301891055</v>
+        <v>0.0002937077301891076</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0004350069504416118</v>
+        <v>0.0004350069504416139</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.000762050148864056</v>
+        <v>0.0007620501488640574</v>
       </c>
     </row>
     <row r="4">
@@ -6918,82 +6918,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0028141512560915</v>
+        <v>0.002814151256091503</v>
       </c>
       <c r="C4" t="n">
         <v>0.002841837965176638</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002961585989262298</v>
+        <v>0.0029615859892623</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002901926882006373</v>
+        <v>0.002901926882006374</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002861291693584854</v>
+        <v>0.002861291693584853</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003348687934286934</v>
+        <v>0.003348687934286936</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002866305603133179</v>
+        <v>0.002866305603133182</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00290902680596633</v>
+        <v>0.002909026805966334</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003167296120606144</v>
+        <v>0.003167296120606147</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003006928313983421</v>
+        <v>0.003006928313983423</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003318057825973155</v>
+        <v>0.003318057825973159</v>
       </c>
       <c r="M4" t="n">
         <v>0.003130634291452548</v>
       </c>
       <c r="N4" t="n">
-        <v>0.002939975938985667</v>
+        <v>0.002939975938985669</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002897694858480534</v>
+        <v>0.002897694858480537</v>
       </c>
       <c r="P4" t="n">
-        <v>0.003194699024755166</v>
+        <v>0.00319469902475517</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002920805033364475</v>
+        <v>0.002920805033364479</v>
       </c>
       <c r="R4" t="n">
-        <v>0.002993746569922639</v>
+        <v>0.002993746569922641</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002989237066865264</v>
+        <v>0.002989237066865268</v>
       </c>
       <c r="T4" t="n">
-        <v>0.002875418936694461</v>
+        <v>0.002875418936694465</v>
       </c>
       <c r="U4" t="n">
-        <v>0.003124126021023529</v>
+        <v>0.003124126021023534</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002036188856002972</v>
+        <v>0.00203618885600298</v>
       </c>
       <c r="W4" t="n">
-        <v>0.003174796708518605</v>
+        <v>0.003174796708518608</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005597540526901764</v>
+        <v>0.005597540526901769</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.006331228291721683</v>
+        <v>0.006331228291721679</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002925776177370998</v>
+        <v>0.002925776177371</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003080814590950472</v>
+        <v>0.003080814590950476</v>
       </c>
       <c r="AB4" t="n">
         <v>0.02238818635390036</v>
@@ -7006,85 +7006,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00283234180788893</v>
+        <v>0.002832341807888931</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002886821819610121</v>
+        <v>0.002886821819610122</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002882904486733332</v>
+        <v>0.002882904486733335</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002850606940540567</v>
+        <v>0.002850606940540569</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002836760000884494</v>
+        <v>0.002836760000884497</v>
       </c>
       <c r="G5" t="n">
         <v>0.002893388987576918</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002882904486733332</v>
+        <v>0.002882904486733335</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002882904486733332</v>
+        <v>0.002882904486733335</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002754652999228624</v>
+        <v>0.002754652999228631</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002882904486733332</v>
+        <v>0.002882904486733335</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002882904486733332</v>
+        <v>0.002882904486733335</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002880874940161126</v>
+        <v>0.002880874940161125</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002843709951676979</v>
+        <v>0.002843709951676981</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002854480950230898</v>
+        <v>0.0028544809502309</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002851840718221516</v>
+        <v>0.00285184071822152</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002822405087459256</v>
+        <v>0.002822405087459259</v>
       </c>
       <c r="R5" t="n">
-        <v>0.002882904486733332</v>
+        <v>0.002882904486733335</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002882904486733332</v>
+        <v>0.002882904486733335</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002882904486733332</v>
+        <v>0.002882904486733335</v>
       </c>
       <c r="U5" t="n">
-        <v>0.002858196913994663</v>
+        <v>0.002858196913994665</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002019973711452809</v>
+        <v>0.002019973711452813</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002882914423748376</v>
+        <v>0.00288291442374838</v>
       </c>
       <c r="X5" t="n">
-        <v>0.002827039257444846</v>
+        <v>0.002827039257444848</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.00293312887422489</v>
+        <v>0.002933128874224893</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.002831402580170508</v>
+        <v>0.00283140258017051</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002882904486733332</v>
+        <v>0.002882904486733335</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003117857504658999</v>
+        <v>0.003117857504659002</v>
       </c>
     </row>
     <row r="6">
@@ -7094,82 +7094,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0001492630546926225</v>
+        <v>0.0001492630546926243</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001769497637777617</v>
+        <v>0.0001769497637777615</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0002966977878634199</v>
+        <v>0.0002966977878634212</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0002370386806074967</v>
+        <v>0.0002370386806074968</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0001964034921859803</v>
+        <v>0.0001964034921859802</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0006738813939268586</v>
+        <v>0.00067388139392686</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0002014174017343045</v>
+        <v>0.0002014174017343054</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0002441386045674566</v>
+        <v>0.0002441386045674581</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000619218723200051</v>
+        <v>0.0006192187232000522</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0003420401125845471</v>
+        <v>0.0003420401125845485</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0006531696245742784</v>
+        <v>0.0006531696245742802</v>
       </c>
       <c r="M6" t="n">
         <v>0.0004657460900536733</v>
       </c>
       <c r="N6" t="n">
-        <v>0.000275087737586793</v>
+        <v>0.0002750877375867954</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0002228883181204581</v>
+        <v>0.0002228883181204603</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0005198924843950905</v>
+        <v>0.0005198924843950928</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0002559168319655998</v>
+        <v>0.000255916831965601</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0003288583685237611</v>
+        <v>0.0003288583685237623</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0003243488654663878</v>
+        <v>0.0003243488654663893</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0002105307352955877</v>
+        <v>0.0002105307352955902</v>
       </c>
       <c r="U6" t="n">
-        <v>0.000449319480663454</v>
+        <v>0.0004493194806634568</v>
       </c>
       <c r="V6" t="n">
         <v>0.0002048854130542903</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0004999901681585295</v>
+        <v>0.0004999901681585314</v>
       </c>
       <c r="X6" t="n">
         <v>0.00292273398654169</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.003666340090322808</v>
+        <v>0.003666340090322807</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0002608879759721238</v>
+        <v>0.000260887975972125</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0004159263895515971</v>
+        <v>0.0004159263895515985</v>
       </c>
       <c r="AB6" t="n">
         <v>0.01972329815250149</v>
@@ -7182,13 +7182,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001674536064900521</v>
+        <v>0.0001674536064900524</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000221933618211247</v>
+        <v>0.0002219336182112473</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0002180162853344573</v>
+        <v>0.0002180162853344575</v>
       </c>
       <c r="E7" t="n">
         <v>0.000185718739141691</v>
@@ -7197,70 +7197,70 @@
         <v>0.0001718717994856179</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002185824472168435</v>
+        <v>0.000218582447216845</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0002180162853344573</v>
+        <v>0.0002180162853344575</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002180162853344573</v>
+        <v>0.0002180162853344575</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0002065756018225332</v>
+        <v>0.0002065756018225342</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0002180162853344573</v>
+        <v>0.0002180162853344575</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002180162853344573</v>
+        <v>0.0002180162853344575</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002159867387622483</v>
+        <v>0.0002159867387622484</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0001788217502781075</v>
+        <v>0.000178821750278107</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001796744098708229</v>
+        <v>0.0001796744098708242</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001770341778614396</v>
+        <v>0.0001770341778614409</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001575168860603831</v>
+        <v>0.000157516886060384</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0002180162853344573</v>
+        <v>0.0002180162853344575</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0002180162853344573</v>
+        <v>0.0002180162853344575</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0002180162853344573</v>
+        <v>0.0002180162853344575</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001833903736345907</v>
+        <v>0.0001833903736345917</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0001886702685041265</v>
+        <v>0.0001886702685041268</v>
       </c>
       <c r="W7" t="n">
-        <v>0.000208107883388305</v>
+        <v>0.0002081078833883066</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0001522327170847702</v>
+        <v>0.0001522327170847726</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0002682406728260161</v>
+        <v>0.0002682406728260164</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001665143787716322</v>
+        <v>0.0001665143787716333</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0002180162853344573</v>
+        <v>0.0002180162853344575</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0004529693032601263</v>
+        <v>0.0004529693032601264</v>
       </c>
     </row>
   </sheetData>
